--- a/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.14.0</t>
+    <t>0.15.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-13T13:47:03+00:00</t>
+    <t>2024-01-14T11:16:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.15.0</t>
+    <t>0.16.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-14T11:16:16+00:00</t>
+    <t>2024-02-08T09:36:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-08T09:36:20+00:00</t>
+    <t>2024-02-09T16:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-09T16:38:59+00:00</t>
+    <t>2024-02-11T14:24:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -754,7 +754,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Procedure)
+    <t xml:space="preserve">Reference(MedicationAdministration|MedicationDispense|MedicationStatement|Procedure|Immunization|ImagingStudy)
 </t>
   </si>
   <si>
@@ -2008,7 +2008,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="110.76953125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="111.11328125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.16.0</t>
+    <t>0.17.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-11T14:24:24+00:00</t>
+    <t>2024-02-12T08:51:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.17.0</t>
+    <t>0.18.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T08:51:11+00:00</t>
+    <t>2024-02-13T17:27:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.18.0</t>
+    <t>0.19.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T17:27:52+00:00</t>
+    <t>2024-02-13T18:57:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T18:57:41+00:00</t>
+    <t>2024-02-13T19:55:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.19.0</t>
+    <t>0.20.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T19:55:01+00:00</t>
+    <t>2024-02-17T09:04:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.20.0</t>
+    <t>0.21.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-17T09:04:28+00:00</t>
+    <t>2024-02-17T09:43:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.21.0</t>
+    <t>0.22.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-17T09:43:43+00:00</t>
+    <t>2024-02-18T11:03:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.22.0</t>
+    <t>0.23.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-18T11:03:00+00:00</t>
+    <t>2024-02-23T15:31:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.23.0</t>
+    <t>0.24.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-23T15:31:48+00:00</t>
+    <t>2024-02-28T12:35:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.24.0</t>
+    <t>0.26.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-28T12:35:36+00:00</t>
+    <t>2024-03-08T13:22:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.26.0</t>
+    <t>0.27.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-08T13:22:05+00:00</t>
+    <t>2024-03-08T18:48:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.27.0</t>
+    <t>0.28.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-08T18:48:53+00:00</t>
+    <t>2024-03-09T10:17:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.28.0</t>
+    <t>0.30.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-09T10:17:01+00:00</t>
+    <t>2024-03-21T09:40:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -237,6 +237,12 @@
     <t>Constraint(s)</t>
   </si>
   <si>
+    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
+  </si>
+  <si>
+    <t>Mapping: Clinical Data Warehouse (CDW)</t>
+  </si>
+  <si>
     <t>Mapping: Workflow Pattern</t>
   </si>
   <si>
@@ -253,12 +259,6 @@
   </si>
   <si>
     <t>Mapping: SNOMED CT Attribute Binding</t>
-  </si>
-  <si>
-    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
-  </si>
-  <si>
-    <t>Mapping: Clinical Data Warehouse (CDW)</t>
   </si>
   <si>
     <t>Vital Signs
@@ -662,13 +662,13 @@
     <t>Identifier.value</t>
   </si>
   <si>
+    <t>1619: source value from RAD/NUC MED REPORTS - IEN (#74-.001)</t>
+  </si>
+  <si>
     <t>CX.1 / EI.1</t>
   </si>
   <si>
     <t>II.extension or II.root if system indicates OID or GUID (Or Role.id.extension or root)</t>
-  </si>
-  <si>
-    <t>1619: source value from RAD/NUC MED REPORTS - IEN (#74-.001)</t>
   </si>
   <si>
     <t>Observation.identifier.period</t>
@@ -767,6 +767,9 @@
     <t>To link an Observation to an Encounter use `encounter`.  See the  [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below for guidance on referencing another Observation.</t>
   </si>
   <si>
+    <t>1620: reference from REGISTERED EXAMS - EXAMINATIONS (#70.02-50)</t>
+  </si>
+  <si>
     <t>Event.partOf</t>
   </si>
   <si>
@@ -776,9 +779,6 @@
     <t>.outboundRelationship[typeCode=FLFS].target</t>
   </si>
   <si>
-    <t>1620: reference from REGISTERED EXAMS - EXAMINATIONS (#70.02-50)</t>
-  </si>
-  <si>
     <t>Observation.status</t>
   </si>
   <si>
@@ -797,6 +797,12 @@
     <t>http://va.gov/fhir/ValueSet/VSVFImageStatusRadNuc</t>
   </si>
   <si>
+    <t>1623: terminologyMaps using VF_ImageStatusRadNuc on RAD/NUC MED REPORTS - REPORT STATUS (#74-5)</t>
+  </si>
+  <si>
+    <t>SStaff.RadiologyNuclearMedicineReport.ReportStatus</t>
+  </si>
+  <si>
     <t>Event.status</t>
   </si>
   <si>
@@ -810,12 +816,6 @@
   </si>
   <si>
     <t>FiveWs.status</t>
-  </si>
-  <si>
-    <t>1623: terminologyMaps using VF_ImageStatusRadNuc on RAD/NUC MED REPORTS - REPORT STATUS (#74-5)</t>
-  </si>
-  <si>
-    <t>SStaff.RadiologyNuclearMedicineReport.ReportStatus</t>
   </si>
   <si>
     <t>Observation.category</t>
@@ -922,6 +922,9 @@
     <t>Observations have no value if you don't know who or what they're about.</t>
   </si>
   <si>
+    <t>1633: reference from RAD/NUC MED REPORTS - PATIENT NAME (#74-2)</t>
+  </si>
+  <si>
     <t>Event.subject</t>
   </si>
   <si>
@@ -932,9 +935,6 @@
   </si>
   <si>
     <t>FiveWs.subject</t>
-  </si>
-  <si>
-    <t>1633: reference from RAD/NUC MED REPORTS - PATIENT NAME (#74-2)</t>
   </si>
   <si>
     <t>Observation.focus</t>
@@ -1070,6 +1070,12 @@
     <t>For Observations that don’t require review and verification, it may be the same as the [`lastUpdated` ](http://hl7.org/fhir/R4/resource-definitions.html#Meta.lastUpdated) time of the resource itself.  For Observations that do require review and verification for certain updates, it might not be the same as the `lastUpdated` time of the resource itself due to a non-clinically significant update that doesn’t require the new version to be reviewed and verified again.</t>
   </si>
   <si>
+    <t>1639: source value from RAD/NUC MED REPORTS - VERIFIED DATE (#74-7)</t>
+  </si>
+  <si>
+    <t>SStaff.RadiologyNuclearMedicineReport.VerifiedDateTime</t>
+  </si>
+  <si>
     <t>OBR.22 (or MSH.7), or perhaps OBX-19 (depends on who observation made)</t>
   </si>
   <si>
@@ -1077,12 +1083,6 @@
   </si>
   <si>
     <t>FiveWs.recorded</t>
-  </si>
-  <si>
-    <t>1639: source value from RAD/NUC MED REPORTS - VERIFIED DATE (#74-7)</t>
-  </si>
-  <si>
-    <t>SStaff.RadiologyNuclearMedicineReport.VerifiedDateTime</t>
   </si>
   <si>
     <t>Observation.performer</t>
@@ -1101,6 +1101,9 @@
     <t>May give a degree of confidence in the observation and also indicates where follow-up questions should be directed.</t>
   </si>
   <si>
+    <t>1642: source value from RAD/NUC MED REPORTS - VERIFYING PHYSICIAN (#74-9)</t>
+  </si>
+  <si>
     <t>Event.performer.actor</t>
   </si>
   <si>
@@ -1111,9 +1114,6 @@
   </si>
   <si>
     <t>FiveWs.actor</t>
-  </si>
-  <si>
-    <t>1642: source value from RAD/NUC MED REPORTS - VERIFYING PHYSICIAN (#74-9)</t>
   </si>
   <si>
     <t>Observation.value[x]</t>
@@ -2033,14 +2033,14 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="247.40625" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="107.01953125" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="42.34375" customWidth="true" bestFit="true"/>
-    <col min="43" max="43" width="124.171875" customWidth="true" bestFit="true"/>
-    <col min="44" max="44" width="54.1640625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="124.171875" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="54.1640625" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="247.40625" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="107.01953125" customWidth="true" bestFit="true"/>
+    <col min="43" max="43" width="36.91796875" customWidth="true" bestFit="true"/>
+    <col min="44" max="44" width="42.34375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2279,22 +2279,22 @@
         <v>88</v>
       </c>
       <c r="AK2" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL2" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM2" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="AL2" t="s" s="2">
+      <c r="AN2" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="AM2" t="s" s="2">
+      <c r="AO2" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="AN2" t="s" s="2">
+      <c r="AP2" t="s" s="2">
         <v>92</v>
-      </c>
-      <c r="AO2" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP2" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ2" t="s" s="2">
         <v>84</v>
@@ -2916,13 +2916,13 @@
         <v>84</v>
       </c>
       <c r="AN7" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO7" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP7" t="s" s="2">
         <v>129</v>
-      </c>
-      <c r="AO7" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP7" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ7" t="s" s="2">
         <v>84</v>
@@ -3042,13 +3042,13 @@
         <v>84</v>
       </c>
       <c r="AN8" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO8" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP8" t="s" s="2">
         <v>137</v>
-      </c>
-      <c r="AO8" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP8" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ8" t="s" s="2">
         <v>84</v>
@@ -3168,13 +3168,13 @@
         <v>84</v>
       </c>
       <c r="AN9" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO9" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP9" t="s" s="2">
         <v>137</v>
-      </c>
-      <c r="AO9" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP9" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ9" t="s" s="2">
         <v>84</v>
@@ -3296,13 +3296,13 @@
         <v>84</v>
       </c>
       <c r="AN10" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO10" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP10" t="s" s="2">
         <v>137</v>
-      </c>
-      <c r="AO10" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP10" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ10" t="s" s="2">
         <v>84</v>
@@ -3413,25 +3413,25 @@
         <v>106</v>
       </c>
       <c r="AK11" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL11" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM11" t="s" s="2">
         <v>156</v>
       </c>
-      <c r="AL11" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM11" t="s" s="2">
+      <c r="AN11" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO11" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="AN11" t="s" s="2">
+      <c r="AP11" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="AO11" t="s" s="2">
+      <c r="AQ11" t="s" s="2">
         <v>159</v>
-      </c>
-      <c r="AP11" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ11" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AR11" t="s" s="2">
         <v>84</v>
@@ -3546,13 +3546,13 @@
         <v>84</v>
       </c>
       <c r="AN12" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO12" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP12" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="AO12" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP12" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ12" t="s" s="2">
         <v>84</v>
@@ -3672,13 +3672,13 @@
         <v>84</v>
       </c>
       <c r="AN13" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO13" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP13" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="AO13" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP13" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ13" t="s" s="2">
         <v>84</v>
@@ -3797,16 +3797,16 @@
         <v>84</v>
       </c>
       <c r="AM14" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN14" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO14" t="s" s="2">
         <v>137</v>
       </c>
-      <c r="AN14" t="s" s="2">
+      <c r="AP14" t="s" s="2">
         <v>181</v>
-      </c>
-      <c r="AO14" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP14" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ14" t="s" s="2">
         <v>84</v>
@@ -3925,16 +3925,16 @@
         <v>84</v>
       </c>
       <c r="AM15" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN15" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO15" t="s" s="2">
         <v>192</v>
       </c>
-      <c r="AN15" t="s" s="2">
+      <c r="AP15" t="s" s="2">
         <v>181</v>
-      </c>
-      <c r="AO15" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP15" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ15" t="s" s="2">
         <v>84</v>
@@ -4053,16 +4053,16 @@
         <v>84</v>
       </c>
       <c r="AM16" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN16" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO16" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="AN16" t="s" s="2">
+      <c r="AP16" t="s" s="2">
         <v>201</v>
-      </c>
-      <c r="AO16" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP16" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ16" t="s" s="2">
         <v>84</v>
@@ -4173,25 +4173,25 @@
         <v>106</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>84</v>
+        <v>208</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>208</v>
+        <v>84</v>
       </c>
       <c r="AN17" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO17" t="s" s="2">
         <v>209</v>
       </c>
-      <c r="AO17" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="AP17" t="s" s="2">
-        <v>84</v>
+        <v>210</v>
       </c>
       <c r="AQ17" t="s" s="2">
-        <v>210</v>
+        <v>84</v>
       </c>
       <c r="AR17" t="s" s="2">
         <v>84</v>
@@ -4303,16 +4303,16 @@
         <v>84</v>
       </c>
       <c r="AM18" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN18" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO18" t="s" s="2">
         <v>216</v>
       </c>
-      <c r="AN18" t="s" s="2">
+      <c r="AP18" t="s" s="2">
         <v>217</v>
-      </c>
-      <c r="AO18" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP18" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ18" t="s" s="2">
         <v>84</v>
@@ -4429,16 +4429,16 @@
         <v>84</v>
       </c>
       <c r="AM19" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN19" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO19" t="s" s="2">
         <v>224</v>
       </c>
-      <c r="AN19" t="s" s="2">
+      <c r="AP19" t="s" s="2">
         <v>225</v>
-      </c>
-      <c r="AO19" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP19" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ19" t="s" s="2">
         <v>84</v>
@@ -4549,22 +4549,22 @@
         <v>106</v>
       </c>
       <c r="AK20" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL20" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM20" t="s" s="2">
         <v>232</v>
       </c>
-      <c r="AL20" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM20" t="s" s="2">
+      <c r="AN20" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO20" t="s" s="2">
         <v>233</v>
       </c>
-      <c r="AN20" t="s" s="2">
+      <c r="AP20" t="s" s="2">
         <v>234</v>
-      </c>
-      <c r="AO20" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP20" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ20" t="s" s="2">
         <v>84</v>
@@ -4684,16 +4684,16 @@
         <v>242</v>
       </c>
       <c r="AN21" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO21" t="s" s="2">
         <v>243</v>
       </c>
-      <c r="AO21" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="AP21" t="s" s="2">
-        <v>84</v>
+        <v>244</v>
       </c>
       <c r="AQ21" t="s" s="2">
-        <v>244</v>
+        <v>84</v>
       </c>
       <c r="AR21" t="s" s="2">
         <v>84</v>
@@ -4816,13 +4816,13 @@
         <v>255</v>
       </c>
       <c r="AP22" t="s" s="2">
-        <v>84</v>
+        <v>256</v>
       </c>
       <c r="AQ22" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AR22" t="s" s="2">
-        <v>257</v>
+        <v>84</v>
       </c>
     </row>
     <row r="23" hidden="true">
@@ -4936,16 +4936,16 @@
         <v>84</v>
       </c>
       <c r="AN23" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO23" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP23" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="AO23" t="s" s="2">
+      <c r="AQ23" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="AP23" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ23" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AR23" t="s" s="2">
         <v>84</v>
@@ -5066,16 +5066,16 @@
         <v>84</v>
       </c>
       <c r="AN24" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO24" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP24" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="AO24" t="s" s="2">
+      <c r="AQ24" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="AP24" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ24" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AR24" t="s" s="2">
         <v>84</v>
@@ -5183,28 +5183,28 @@
         <v>106</v>
       </c>
       <c r="AK25" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL25" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM25" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="AL25" t="s" s="2">
+      <c r="AN25" t="s" s="2">
         <v>279</v>
       </c>
-      <c r="AM25" t="s" s="2">
+      <c r="AO25" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="AN25" t="s" s="2">
+      <c r="AP25" t="s" s="2">
         <v>281</v>
       </c>
-      <c r="AO25" t="s" s="2">
+      <c r="AQ25" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="AP25" t="s" s="2">
+      <c r="AR25" t="s" s="2">
         <v>283</v>
-      </c>
-      <c r="AQ25" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR25" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="26" hidden="true">
@@ -5320,13 +5320,13 @@
         <v>291</v>
       </c>
       <c r="AN26" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO26" t="s" s="2">
         <v>292</v>
       </c>
-      <c r="AO26" t="s" s="2">
+      <c r="AP26" t="s" s="2">
         <v>293</v>
-      </c>
-      <c r="AP26" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ26" t="s" s="2">
         <v>294</v>
@@ -5443,19 +5443,19 @@
         <v>84</v>
       </c>
       <c r="AM27" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN27" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO27" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="AN27" t="s" s="2">
+      <c r="AP27" t="s" s="2">
         <v>300</v>
       </c>
-      <c r="AO27" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="AP27" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="AQ27" t="s" s="2">
-        <v>84</v>
+        <v>294</v>
       </c>
       <c r="AR27" t="s" s="2">
         <v>84</v>
@@ -5565,25 +5565,25 @@
         <v>106</v>
       </c>
       <c r="AK28" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL28" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM28" t="s" s="2">
         <v>308</v>
       </c>
-      <c r="AL28" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM28" t="s" s="2">
+      <c r="AN28" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO28" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="AN28" t="s" s="2">
+      <c r="AP28" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="AO28" t="s" s="2">
+      <c r="AQ28" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="AP28" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ28" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AR28" t="s" s="2">
         <v>84</v>
@@ -5691,25 +5691,25 @@
         <v>321</v>
       </c>
       <c r="AK29" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL29" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM29" t="s" s="2">
         <v>322</v>
       </c>
-      <c r="AL29" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM29" t="s" s="2">
+      <c r="AN29" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO29" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="AN29" t="s" s="2">
+      <c r="AP29" t="s" s="2">
         <v>324</v>
       </c>
-      <c r="AO29" t="s" s="2">
+      <c r="AQ29" t="s" s="2">
         <v>325</v>
-      </c>
-      <c r="AP29" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ29" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AR29" t="s" s="2">
         <v>84</v>
@@ -5821,28 +5821,28 @@
         <v>321</v>
       </c>
       <c r="AK30" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="AL30" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="AM30" t="s" s="2">
         <v>322</v>
       </c>
-      <c r="AL30" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM30" t="s" s="2">
+      <c r="AN30" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO30" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="AN30" t="s" s="2">
+      <c r="AP30" t="s" s="2">
         <v>324</v>
       </c>
-      <c r="AO30" t="s" s="2">
+      <c r="AQ30" t="s" s="2">
         <v>325</v>
       </c>
-      <c r="AP30" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ30" t="s" s="2">
-        <v>329</v>
-      </c>
       <c r="AR30" t="s" s="2">
-        <v>330</v>
+        <v>84</v>
       </c>
     </row>
     <row r="31" hidden="true">
@@ -5947,28 +5947,28 @@
         <v>106</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>84</v>
+        <v>336</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>84</v>
+        <v>337</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>336</v>
+        <v>84</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>337</v>
+        <v>84</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>338</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>84</v>
+        <v>339</v>
       </c>
       <c r="AQ31" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AR31" t="s" s="2">
-        <v>340</v>
+        <v>84</v>
       </c>
     </row>
     <row r="32" hidden="true">
@@ -6082,13 +6082,13 @@
         <v>347</v>
       </c>
       <c r="AN32" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO32" t="s" s="2">
         <v>348</v>
       </c>
-      <c r="AO32" t="s" s="2">
+      <c r="AP32" t="s" s="2">
         <v>349</v>
-      </c>
-      <c r="AP32" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ32" t="s" s="2">
         <v>350</v>
@@ -6202,25 +6202,25 @@
         <v>84</v>
       </c>
       <c r="AL33" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM33" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN33" t="s" s="2">
         <v>359</v>
       </c>
-      <c r="AM33" t="s" s="2">
+      <c r="AO33" t="s" s="2">
         <v>360</v>
       </c>
-      <c r="AN33" t="s" s="2">
+      <c r="AP33" t="s" s="2">
         <v>361</v>
       </c>
-      <c r="AO33" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP33" t="s" s="2">
+      <c r="AQ33" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR33" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="AQ33" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR33" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="34" hidden="true">
@@ -6329,28 +6329,28 @@
         <v>358</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>84</v>
+        <v>365</v>
       </c>
       <c r="AL34" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="AM34" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN34" t="s" s="2">
         <v>359</v>
       </c>
-      <c r="AM34" t="s" s="2">
+      <c r="AO34" t="s" s="2">
         <v>360</v>
       </c>
-      <c r="AN34" t="s" s="2">
+      <c r="AP34" t="s" s="2">
         <v>361</v>
       </c>
-      <c r="AO34" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP34" t="s" s="2">
+      <c r="AQ34" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR34" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="AQ34" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="AR34" t="s" s="2">
-        <v>366</v>
       </c>
     </row>
     <row r="35" hidden="true">
@@ -6463,16 +6463,16 @@
         <v>84</v>
       </c>
       <c r="AM35" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN35" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO35" t="s" s="2">
         <v>137</v>
       </c>
-      <c r="AN35" t="s" s="2">
+      <c r="AP35" t="s" s="2">
         <v>375</v>
-      </c>
-      <c r="AO35" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP35" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ35" t="s" s="2">
         <v>84</v>
@@ -6588,25 +6588,25 @@
         <v>84</v>
       </c>
       <c r="AL36" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM36" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN36" t="s" s="2">
         <v>384</v>
       </c>
-      <c r="AM36" t="s" s="2">
+      <c r="AO36" t="s" s="2">
         <v>385</v>
       </c>
-      <c r="AN36" t="s" s="2">
+      <c r="AP36" t="s" s="2">
         <v>386</v>
       </c>
-      <c r="AO36" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP36" t="s" s="2">
+      <c r="AQ36" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR36" t="s" s="2">
         <v>387</v>
-      </c>
-      <c r="AQ36" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR36" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="37" hidden="true">
@@ -6719,16 +6719,16 @@
         <v>84</v>
       </c>
       <c r="AM37" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN37" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO37" t="s" s="2">
         <v>394</v>
       </c>
-      <c r="AN37" t="s" s="2">
+      <c r="AP37" t="s" s="2">
         <v>395</v>
-      </c>
-      <c r="AO37" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP37" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ37" t="s" s="2">
         <v>84</v>
@@ -6842,25 +6842,25 @@
         <v>84</v>
       </c>
       <c r="AL38" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM38" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN38" t="s" s="2">
         <v>403</v>
       </c>
-      <c r="AM38" t="s" s="2">
+      <c r="AO38" t="s" s="2">
         <v>404</v>
       </c>
-      <c r="AN38" t="s" s="2">
+      <c r="AP38" t="s" s="2">
         <v>405</v>
       </c>
-      <c r="AO38" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP38" t="s" s="2">
+      <c r="AQ38" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR38" t="s" s="2">
         <v>406</v>
-      </c>
-      <c r="AQ38" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR38" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="39" hidden="true">
@@ -6973,16 +6973,16 @@
         <v>84</v>
       </c>
       <c r="AM39" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN39" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO39" t="s" s="2">
         <v>414</v>
       </c>
-      <c r="AN39" t="s" s="2">
+      <c r="AP39" t="s" s="2">
         <v>415</v>
-      </c>
-      <c r="AO39" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP39" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ39" t="s" s="2">
         <v>84</v>
@@ -7096,25 +7096,25 @@
         <v>84</v>
       </c>
       <c r="AL40" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM40" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN40" t="s" s="2">
         <v>421</v>
       </c>
-      <c r="AM40" t="s" s="2">
+      <c r="AO40" t="s" s="2">
         <v>422</v>
       </c>
-      <c r="AN40" t="s" s="2">
+      <c r="AP40" t="s" s="2">
         <v>423</v>
       </c>
-      <c r="AO40" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP40" t="s" s="2">
+      <c r="AQ40" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR40" t="s" s="2">
         <v>424</v>
-      </c>
-      <c r="AQ40" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR40" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="41" hidden="true">
@@ -7222,25 +7222,25 @@
         <v>84</v>
       </c>
       <c r="AL41" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM41" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN41" t="s" s="2">
         <v>430</v>
       </c>
-      <c r="AM41" t="s" s="2">
+      <c r="AO41" t="s" s="2">
         <v>431</v>
       </c>
-      <c r="AN41" t="s" s="2">
+      <c r="AP41" t="s" s="2">
         <v>432</v>
       </c>
-      <c r="AO41" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP41" t="s" s="2">
+      <c r="AQ41" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR41" t="s" s="2">
         <v>433</v>
-      </c>
-      <c r="AQ41" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR41" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="42" hidden="true">
@@ -7353,16 +7353,16 @@
         <v>84</v>
       </c>
       <c r="AM42" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN42" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO42" t="s" s="2">
         <v>441</v>
       </c>
-      <c r="AN42" t="s" s="2">
+      <c r="AP42" t="s" s="2">
         <v>442</v>
-      </c>
-      <c r="AO42" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP42" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ42" t="s" s="2">
         <v>84</v>
@@ -7480,13 +7480,13 @@
         <v>84</v>
       </c>
       <c r="AN43" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO43" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP43" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="AO43" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP43" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ43" t="s" s="2">
         <v>84</v>
@@ -7606,13 +7606,13 @@
         <v>84</v>
       </c>
       <c r="AN44" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO44" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP44" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="AO44" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP44" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ44" t="s" s="2">
         <v>84</v>
@@ -7734,13 +7734,13 @@
         <v>84</v>
       </c>
       <c r="AN45" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO45" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP45" t="s" s="2">
         <v>137</v>
-      </c>
-      <c r="AO45" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP45" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ45" t="s" s="2">
         <v>84</v>
@@ -7855,16 +7855,16 @@
         <v>84</v>
       </c>
       <c r="AM46" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN46" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO46" t="s" s="2">
         <v>455</v>
       </c>
-      <c r="AN46" t="s" s="2">
+      <c r="AP46" t="s" s="2">
         <v>456</v>
-      </c>
-      <c r="AO46" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP46" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ46" t="s" s="2">
         <v>84</v>
@@ -7979,16 +7979,16 @@
         <v>84</v>
       </c>
       <c r="AM47" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN47" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO47" t="s" s="2">
         <v>455</v>
       </c>
-      <c r="AN47" t="s" s="2">
+      <c r="AP47" t="s" s="2">
         <v>460</v>
-      </c>
-      <c r="AO47" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP47" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ47" t="s" s="2">
         <v>84</v>
@@ -8104,19 +8104,19 @@
         <v>84</v>
       </c>
       <c r="AL48" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM48" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN48" t="s" s="2">
         <v>468</v>
       </c>
-      <c r="AM48" t="s" s="2">
+      <c r="AO48" t="s" s="2">
         <v>469</v>
       </c>
-      <c r="AN48" t="s" s="2">
+      <c r="AP48" t="s" s="2">
         <v>386</v>
-      </c>
-      <c r="AO48" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP48" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ48" t="s" s="2">
         <v>84</v>
@@ -8232,19 +8232,19 @@
         <v>84</v>
       </c>
       <c r="AL49" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM49" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN49" t="s" s="2">
         <v>468</v>
       </c>
-      <c r="AM49" t="s" s="2">
+      <c r="AO49" t="s" s="2">
         <v>469</v>
       </c>
-      <c r="AN49" t="s" s="2">
+      <c r="AP49" t="s" s="2">
         <v>386</v>
-      </c>
-      <c r="AO49" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP49" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ49" t="s" s="2">
         <v>84</v>
@@ -8364,13 +8364,13 @@
         <v>84</v>
       </c>
       <c r="AN50" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO50" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP50" t="s" s="2">
         <v>482</v>
-      </c>
-      <c r="AO50" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP50" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ50" t="s" s="2">
         <v>84</v>
@@ -8485,16 +8485,16 @@
         <v>84</v>
       </c>
       <c r="AM51" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN51" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO51" t="s" s="2">
         <v>455</v>
       </c>
-      <c r="AN51" t="s" s="2">
+      <c r="AP51" t="s" s="2">
         <v>486</v>
-      </c>
-      <c r="AO51" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP51" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ51" t="s" s="2">
         <v>84</v>
@@ -8611,16 +8611,16 @@
         <v>84</v>
       </c>
       <c r="AM52" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN52" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO52" t="s" s="2">
         <v>492</v>
       </c>
-      <c r="AN52" t="s" s="2">
+      <c r="AP52" t="s" s="2">
         <v>493</v>
-      </c>
-      <c r="AO52" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP52" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ52" t="s" s="2">
         <v>84</v>
@@ -8737,16 +8737,16 @@
         <v>84</v>
       </c>
       <c r="AM53" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN53" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO53" t="s" s="2">
         <v>492</v>
       </c>
-      <c r="AN53" t="s" s="2">
+      <c r="AP53" t="s" s="2">
         <v>499</v>
-      </c>
-      <c r="AO53" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP53" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ53" t="s" s="2">
         <v>84</v>
@@ -8865,16 +8865,16 @@
         <v>84</v>
       </c>
       <c r="AM54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO54" t="s" s="2">
         <v>505</v>
       </c>
-      <c r="AN54" t="s" s="2">
+      <c r="AP54" t="s" s="2">
         <v>506</v>
-      </c>
-      <c r="AO54" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP54" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ54" t="s" s="2">
         <v>84</v>
@@ -8992,13 +8992,13 @@
         <v>84</v>
       </c>
       <c r="AN55" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO55" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP55" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="AO55" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP55" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ55" t="s" s="2">
         <v>84</v>
@@ -9118,13 +9118,13 @@
         <v>84</v>
       </c>
       <c r="AN56" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO56" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP56" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="AO56" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP56" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ56" t="s" s="2">
         <v>84</v>
@@ -9246,13 +9246,13 @@
         <v>84</v>
       </c>
       <c r="AN57" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO57" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP57" t="s" s="2">
         <v>137</v>
-      </c>
-      <c r="AO57" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP57" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ57" t="s" s="2">
         <v>84</v>
@@ -9368,22 +9368,22 @@
         <v>84</v>
       </c>
       <c r="AL58" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM58" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN58" t="s" s="2">
         <v>516</v>
       </c>
-      <c r="AM58" t="s" s="2">
+      <c r="AO58" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="AN58" t="s" s="2">
+      <c r="AP58" t="s" s="2">
         <v>281</v>
       </c>
-      <c r="AO58" t="s" s="2">
+      <c r="AQ58" t="s" s="2">
         <v>282</v>
-      </c>
-      <c r="AP58" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ58" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AR58" t="s" s="2">
         <v>84</v>
@@ -9496,25 +9496,25 @@
         <v>84</v>
       </c>
       <c r="AL59" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM59" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN59" t="s" s="2">
         <v>520</v>
       </c>
-      <c r="AM59" t="s" s="2">
+      <c r="AO59" t="s" s="2">
         <v>360</v>
       </c>
-      <c r="AN59" t="s" s="2">
+      <c r="AP59" t="s" s="2">
         <v>361</v>
       </c>
-      <c r="AO59" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP59" t="s" s="2">
+      <c r="AQ59" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR59" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="AQ59" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR59" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="60" hidden="true">
@@ -9627,16 +9627,16 @@
         <v>84</v>
       </c>
       <c r="AM60" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN60" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO60" t="s" s="2">
         <v>137</v>
       </c>
-      <c r="AN60" t="s" s="2">
+      <c r="AP60" t="s" s="2">
         <v>375</v>
-      </c>
-      <c r="AO60" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP60" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ60" t="s" s="2">
         <v>84</v>
@@ -9752,25 +9752,25 @@
         <v>84</v>
       </c>
       <c r="AL61" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM61" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN61" t="s" s="2">
         <v>384</v>
       </c>
-      <c r="AM61" t="s" s="2">
+      <c r="AO61" t="s" s="2">
         <v>385</v>
       </c>
-      <c r="AN61" t="s" s="2">
+      <c r="AP61" t="s" s="2">
         <v>386</v>
       </c>
-      <c r="AO61" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP61" t="s" s="2">
+      <c r="AQ61" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR61" t="s" s="2">
         <v>387</v>
-      </c>
-      <c r="AQ61" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR61" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="62" hidden="true">
@@ -9883,16 +9883,16 @@
         <v>84</v>
       </c>
       <c r="AM62" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN62" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO62" t="s" s="2">
         <v>441</v>
       </c>
-      <c r="AN62" t="s" s="2">
+      <c r="AP62" t="s" s="2">
         <v>442</v>
-      </c>
-      <c r="AO62" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP62" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ62" t="s" s="2">
         <v>84</v>

--- a/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.30.0</t>
+    <t>0.32.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-21T09:40:56+00:00</t>
+    <t>2024-03-22T16:04:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.32.0</t>
+    <t>0.34.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-22T16:04:14+00:00</t>
+    <t>2024-03-29T18:32:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2540" uniqueCount="530">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2540" uniqueCount="531">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-29T18:32:47+00:00</t>
+    <t>2024-03-30T09:34:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -831,28 +831,6 @@
   </si>
   <si>
     <t>Used for filtering what observations are retrieved and displayed.</t>
-  </si>
-  <si>
-    <t>Codes for high level observation categories.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pattern:$this}
-</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
-  </si>
-  <si>
-    <t>FiveWs.class</t>
-  </si>
-  <si>
-    <t>Observation.category:imaging</t>
-  </si>
-  <si>
-    <t>imaging</t>
   </si>
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
@@ -861,6 +839,31 @@
     &lt;code value="imaging"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
+    <t>Codes for high level observation categories.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pattern:$this}
+</t>
+  </si>
+  <si>
+    <t>1624: fixed value = http://terminology.hl7.org/CodeSystem/observation-category#imaging</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
+  </si>
+  <si>
+    <t>FiveWs.class</t>
+  </si>
+  <si>
+    <t>Observation.category:imaging</t>
+  </si>
+  <si>
+    <t>imaging</t>
   </si>
   <si>
     <t>Observation.code</t>
@@ -4875,7 +4878,7 @@
         <v>84</v>
       </c>
       <c r="S23" t="s" s="2">
-        <v>84</v>
+        <v>263</v>
       </c>
       <c r="T23" t="s" s="2">
         <v>84</v>
@@ -4893,16 +4896,16 @@
         <v>118</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AC23" s="2"/>
       <c r="AD23" t="s" s="2">
@@ -4927,7 +4930,7 @@
         <v>106</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>84</v>
+        <v>267</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>84</v>
@@ -4942,10 +4945,10 @@
         <v>84</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="AQ23" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AR23" t="s" s="2">
         <v>84</v>
@@ -4953,13 +4956,13 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B24" t="s" s="2">
         <v>258</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>84</v>
@@ -5003,7 +5006,7 @@
         <v>84</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="T24" t="s" s="2">
         <v>84</v>
@@ -5021,10 +5024,10 @@
         <v>118</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>84</v>
@@ -5072,10 +5075,10 @@
         <v>84</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="AQ24" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AR24" t="s" s="2">
         <v>84</v>
@@ -5083,14 +5086,14 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -5112,16 +5115,16 @@
         <v>183</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>84</v>
@@ -5150,7 +5153,7 @@
       </c>
       <c r="Y25" s="2"/>
       <c r="Z25" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>84</v>
@@ -5168,7 +5171,7 @@
         <v>84</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>94</v>
@@ -5189,30 +5192,30 @@
         <v>84</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AQ25" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AR25" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5235,19 +5238,19 @@
         <v>95</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>84</v>
@@ -5296,7 +5299,7 @@
         <v>84</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>82</v>
@@ -5311,25 +5314,25 @@
         <v>106</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AQ26" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AR26" t="s" s="2">
         <v>84</v>
@@ -5337,10 +5340,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5363,16 +5366,16 @@
         <v>95</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -5422,7 +5425,7 @@
         <v>84</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>82</v>
@@ -5449,13 +5452,13 @@
         <v>84</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AQ27" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AR27" t="s" s="2">
         <v>84</v>
@@ -5463,14 +5466,14 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -5489,19 +5492,19 @@
         <v>95</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>84</v>
@@ -5550,7 +5553,7 @@
         <v>84</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>82</v>
@@ -5571,19 +5574,19 @@
         <v>84</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AQ28" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AR28" t="s" s="2">
         <v>84</v>
@@ -5591,14 +5594,14 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -5617,19 +5620,19 @@
         <v>95</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>84</v>
@@ -5666,7 +5669,7 @@
         <v>84</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AC29" s="2"/>
       <c r="AD29" t="s" s="2">
@@ -5676,7 +5679,7 @@
         <v>170</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>82</v>
@@ -5685,10 +5688,10 @@
         <v>94</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>84</v>
@@ -5697,19 +5700,19 @@
         <v>84</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AQ29" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AR29" t="s" s="2">
         <v>84</v>
@@ -5717,16 +5720,16 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D30" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -5745,19 +5748,19 @@
         <v>95</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>84</v>
@@ -5806,7 +5809,7 @@
         <v>84</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>82</v>
@@ -5815,31 +5818,31 @@
         <v>94</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AQ30" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AR30" t="s" s="2">
         <v>84</v>
@@ -5847,10 +5850,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5873,16 +5876,16 @@
         <v>95</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5932,7 +5935,7 @@
         <v>84</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>82</v>
@@ -5947,10 +5950,10 @@
         <v>106</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>84</v>
@@ -5959,13 +5962,13 @@
         <v>84</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AQ31" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AR31" t="s" s="2">
         <v>84</v>
@@ -5973,10 +5976,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5999,17 +6002,17 @@
         <v>95</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>84</v>
@@ -6058,7 +6061,7 @@
         <v>84</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>82</v>
@@ -6073,25 +6076,25 @@
         <v>106</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AQ32" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AR32" t="s" s="2">
         <v>84</v>
@@ -6099,10 +6102,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6125,19 +6128,19 @@
         <v>95</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>84</v>
@@ -6174,7 +6177,7 @@
         <v>84</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AC33" s="2"/>
       <c r="AD33" t="s" s="2">
@@ -6184,7 +6187,7 @@
         <v>170</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>82</v>
@@ -6193,10 +6196,10 @@
         <v>94</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>84</v>
@@ -6208,30 +6211,30 @@
         <v>84</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AQ33" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR33" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D34" t="s" s="2">
         <v>84</v>
@@ -6256,16 +6259,16 @@
         <v>161</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>84</v>
@@ -6314,7 +6317,7 @@
         <v>84</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>82</v>
@@ -6323,42 +6326,42 @@
         <v>94</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AQ34" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR34" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6384,16 +6387,16 @@
         <v>183</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>84</v>
@@ -6421,10 +6424,10 @@
         <v>188</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>84</v>
@@ -6442,7 +6445,7 @@
         <v>84</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>82</v>
@@ -6451,7 +6454,7 @@
         <v>94</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AJ35" t="s" s="2">
         <v>106</v>
@@ -6472,7 +6475,7 @@
         <v>137</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AQ35" t="s" s="2">
         <v>84</v>
@@ -6483,14 +6486,14 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
@@ -6512,16 +6515,16 @@
         <v>183</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>84</v>
@@ -6549,10 +6552,10 @@
         <v>188</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>84</v>
@@ -6570,7 +6573,7 @@
         <v>84</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>82</v>
@@ -6594,27 +6597,27 @@
         <v>84</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AQ36" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR36" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6637,19 +6640,19 @@
         <v>84</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>84</v>
@@ -6698,7 +6701,7 @@
         <v>84</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>82</v>
@@ -6725,10 +6728,10 @@
         <v>84</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AQ37" t="s" s="2">
         <v>84</v>
@@ -6739,10 +6742,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6768,13 +6771,13 @@
         <v>183</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6800,13 +6803,13 @@
         <v>84</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>84</v>
@@ -6824,7 +6827,7 @@
         <v>84</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>82</v>
@@ -6848,27 +6851,27 @@
         <v>84</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AQ38" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR38" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6894,16 +6897,16 @@
         <v>183</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>84</v>
@@ -6928,13 +6931,13 @@
         <v>84</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>84</v>
@@ -6952,7 +6955,7 @@
         <v>84</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
@@ -6979,10 +6982,10 @@
         <v>84</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AQ39" t="s" s="2">
         <v>84</v>
@@ -6993,10 +6996,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7019,16 +7022,16 @@
         <v>84</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -7078,7 +7081,7 @@
         <v>84</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>82</v>
@@ -7102,27 +7105,27 @@
         <v>84</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AQ40" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR40" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7145,16 +7148,16 @@
         <v>84</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -7204,7 +7207,7 @@
         <v>84</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
@@ -7228,27 +7231,27 @@
         <v>84</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AQ41" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR41" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7271,19 +7274,19 @@
         <v>84</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>84</v>
@@ -7332,7 +7335,7 @@
         <v>84</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>82</v>
@@ -7344,7 +7347,7 @@
         <v>84</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>84</v>
@@ -7359,10 +7362,10 @@
         <v>84</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AQ42" t="s" s="2">
         <v>84</v>
@@ -7373,10 +7376,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7497,10 +7500,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7623,14 +7626,14 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -7652,10 +7655,10 @@
         <v>140</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="N45" t="s" s="2">
         <v>143</v>
@@ -7710,7 +7713,7 @@
         <v>84</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
@@ -7751,10 +7754,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7777,13 +7780,13 @@
         <v>84</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7834,7 +7837,7 @@
         <v>84</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
@@ -7843,7 +7846,7 @@
         <v>94</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AJ46" t="s" s="2">
         <v>106</v>
@@ -7861,10 +7864,10 @@
         <v>84</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AQ46" t="s" s="2">
         <v>84</v>
@@ -7875,10 +7878,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7901,13 +7904,13 @@
         <v>84</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7958,7 +7961,7 @@
         <v>84</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
@@ -7967,7 +7970,7 @@
         <v>94</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>106</v>
@@ -7985,10 +7988,10 @@
         <v>84</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AQ47" t="s" s="2">
         <v>84</v>
@@ -7999,10 +8002,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8028,16 +8031,16 @@
         <v>183</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>84</v>
@@ -8065,10 +8068,10 @@
         <v>118</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>84</v>
@@ -8086,7 +8089,7 @@
         <v>84</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -8110,13 +8113,13 @@
         <v>84</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AQ48" t="s" s="2">
         <v>84</v>
@@ -8127,10 +8130,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8156,16 +8159,16 @@
         <v>183</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>84</v>
@@ -8190,13 +8193,13 @@
         <v>84</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>84</v>
@@ -8214,7 +8217,7 @@
         <v>84</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
@@ -8238,13 +8241,13 @@
         <v>84</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AQ49" t="s" s="2">
         <v>84</v>
@@ -8255,10 +8258,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8281,17 +8284,17 @@
         <v>84</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>84</v>
@@ -8340,7 +8343,7 @@
         <v>84</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
@@ -8370,7 +8373,7 @@
         <v>84</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AQ50" t="s" s="2">
         <v>84</v>
@@ -8381,10 +8384,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8410,10 +8413,10 @@
         <v>161</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -8464,7 +8467,7 @@
         <v>84</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
@@ -8491,10 +8494,10 @@
         <v>84</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AQ51" t="s" s="2">
         <v>84</v>
@@ -8505,10 +8508,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8531,16 +8534,16 @@
         <v>95</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8590,7 +8593,7 @@
         <v>84</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
@@ -8617,10 +8620,10 @@
         <v>84</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AQ52" t="s" s="2">
         <v>84</v>
@@ -8631,10 +8634,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8657,16 +8660,16 @@
         <v>95</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8716,7 +8719,7 @@
         <v>84</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>82</v>
@@ -8743,10 +8746,10 @@
         <v>84</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AQ53" t="s" s="2">
         <v>84</v>
@@ -8757,10 +8760,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8783,19 +8786,19 @@
         <v>95</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>84</v>
@@ -8844,7 +8847,7 @@
         <v>84</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>82</v>
@@ -8871,10 +8874,10 @@
         <v>84</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AQ54" t="s" s="2">
         <v>84</v>
@@ -8885,10 +8888,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9009,10 +9012,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9135,14 +9138,14 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -9164,10 +9167,10 @@
         <v>140</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="N57" t="s" s="2">
         <v>143</v>
@@ -9222,7 +9225,7 @@
         <v>84</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>82</v>
@@ -9263,10 +9266,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9292,16 +9295,16 @@
         <v>183</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>84</v>
@@ -9326,13 +9329,13 @@
         <v>84</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>84</v>
@@ -9350,7 +9353,7 @@
         <v>84</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>94</v>
@@ -9374,16 +9377,16 @@
         <v>84</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AQ58" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AR58" t="s" s="2">
         <v>84</v>
@@ -9391,10 +9394,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9417,19 +9420,19 @@
         <v>95</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>84</v>
@@ -9478,7 +9481,7 @@
         <v>84</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
@@ -9502,27 +9505,27 @@
         <v>84</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AQ59" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR59" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9548,16 +9551,16 @@
         <v>183</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>84</v>
@@ -9585,10 +9588,10 @@
         <v>188</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>84</v>
@@ -9606,7 +9609,7 @@
         <v>84</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>82</v>
@@ -9615,7 +9618,7 @@
         <v>94</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>106</v>
@@ -9636,7 +9639,7 @@
         <v>137</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AQ60" t="s" s="2">
         <v>84</v>
@@ -9647,14 +9650,14 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
@@ -9676,16 +9679,16 @@
         <v>183</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>84</v>
@@ -9713,10 +9716,10 @@
         <v>188</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>84</v>
@@ -9734,7 +9737,7 @@
         <v>84</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>82</v>
@@ -9758,27 +9761,27 @@
         <v>84</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AQ61" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR61" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9804,16 +9807,16 @@
         <v>85</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>84</v>
@@ -9862,7 +9865,7 @@
         <v>84</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>82</v>
@@ -9889,10 +9892,10 @@
         <v>84</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AQ62" t="s" s="2">
         <v>84</v>

--- a/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$62</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$64</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2540" uniqueCount="531">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2624" uniqueCount="539">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.34.0</t>
+    <t>0.36.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-30T09:34:15+00:00</t>
+    <t>2024-04-03T07:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1170,6 +1170,28 @@
     <t>SPatientText.RadiologyImpressions.ImpressionText</t>
   </si>
   <si>
+    <t>Observation.value[x]:valueQuantity</t>
+  </si>
+  <si>
+    <t>valueQuantity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quantity
+</t>
+  </si>
+  <si>
+    <t>1797: target not supported</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueCodeableConcept</t>
+  </si>
+  <si>
+    <t>valueCodeableConcept</t>
+  </si>
+  <si>
+    <t>1798: target not supported</t>
+  </si>
+  <si>
     <t>Observation.dataAbsentReason</t>
   </si>
   <si>
@@ -1194,6 +1216,9 @@
   <si>
     <t>obs-6
 us-core-2</t>
+  </si>
+  <si>
+    <t>1796: target not supported</t>
   </si>
   <si>
     <t>value.nullFlavor</t>
@@ -1998,12 +2023,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AR62"/>
+  <dimension ref="A1:AR64"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="44.67578125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="44.67578125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="17.96484375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="22.25390625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -6361,9 +6386,11 @@
         <v>368</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="C35" s="2"/>
+        <v>352</v>
+      </c>
+      <c r="C35" t="s" s="2">
+        <v>369</v>
+      </c>
       <c r="D35" t="s" s="2">
         <v>84</v>
       </c>
@@ -6381,22 +6408,22 @@
         <v>84</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>183</v>
+        <v>370</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>369</v>
+        <v>354</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>370</v>
+        <v>355</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>371</v>
+        <v>356</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>372</v>
+        <v>357</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>84</v>
@@ -6421,13 +6448,13 @@
         <v>84</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>188</v>
+        <v>84</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>373</v>
+        <v>84</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>374</v>
+        <v>84</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>84</v>
@@ -6445,7 +6472,7 @@
         <v>84</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>368</v>
+        <v>352</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>82</v>
@@ -6454,13 +6481,13 @@
         <v>94</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>375</v>
+        <v>358</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>106</v>
+        <v>359</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>84</v>
+        <v>371</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>84</v>
@@ -6469,62 +6496,64 @@
         <v>84</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>84</v>
+        <v>360</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>137</v>
+        <v>361</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>376</v>
+        <v>362</v>
       </c>
       <c r="AQ35" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR35" t="s" s="2">
-        <v>84</v>
+        <v>363</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="C36" s="2"/>
+        <v>352</v>
+      </c>
+      <c r="C36" t="s" s="2">
+        <v>373</v>
+      </c>
       <c r="D36" t="s" s="2">
-        <v>378</v>
+        <v>84</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K36" t="s" s="2">
         <v>183</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>379</v>
+        <v>354</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>380</v>
+        <v>355</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>381</v>
+        <v>356</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>382</v>
+        <v>357</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>84</v>
@@ -6549,13 +6578,13 @@
         <v>84</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>188</v>
+        <v>84</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>383</v>
+        <v>84</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>384</v>
+        <v>84</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>84</v>
@@ -6573,22 +6602,22 @@
         <v>84</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>377</v>
+        <v>352</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>84</v>
+        <v>358</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>106</v>
+        <v>359</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>84</v>
+        <v>374</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>84</v>
@@ -6597,27 +6626,27 @@
         <v>84</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>385</v>
+        <v>360</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>386</v>
+        <v>361</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>387</v>
+        <v>362</v>
       </c>
       <c r="AQ36" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR36" t="s" s="2">
-        <v>388</v>
+        <v>363</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>389</v>
+        <v>375</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>389</v>
+        <v>375</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6628,10 +6657,10 @@
         <v>82</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>84</v>
@@ -6640,19 +6669,19 @@
         <v>84</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>390</v>
+        <v>183</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>391</v>
+        <v>376</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>392</v>
+        <v>377</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>393</v>
+        <v>378</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>394</v>
+        <v>379</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>84</v>
@@ -6677,13 +6706,13 @@
         <v>84</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>84</v>
+        <v>188</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>84</v>
+        <v>380</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>84</v>
+        <v>381</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>84</v>
@@ -6701,22 +6730,22 @@
         <v>84</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>389</v>
+        <v>375</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>84</v>
+        <v>382</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>84</v>
+        <v>383</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>84</v>
@@ -6728,10 +6757,10 @@
         <v>84</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>395</v>
+        <v>137</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>396</v>
+        <v>384</v>
       </c>
       <c r="AQ37" t="s" s="2">
         <v>84</v>
@@ -6742,21 +6771,21 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>397</v>
+        <v>385</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>397</v>
+        <v>385</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>84</v>
+        <v>386</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>84</v>
@@ -6771,15 +6800,17 @@
         <v>183</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>398</v>
+        <v>387</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>399</v>
+        <v>388</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="O38" s="2"/>
+        <v>389</v>
+      </c>
+      <c r="O38" t="s" s="2">
+        <v>390</v>
+      </c>
       <c r="P38" t="s" s="2">
         <v>84</v>
       </c>
@@ -6803,13 +6834,13 @@
         <v>84</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>401</v>
+        <v>188</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>402</v>
+        <v>391</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>403</v>
+        <v>392</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>84</v>
@@ -6827,13 +6858,13 @@
         <v>84</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>397</v>
+        <v>385</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>84</v>
@@ -6851,27 +6882,27 @@
         <v>84</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>404</v>
+        <v>393</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>405</v>
+        <v>394</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>406</v>
+        <v>395</v>
       </c>
       <c r="AQ38" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR38" t="s" s="2">
-        <v>407</v>
+        <v>396</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>408</v>
+        <v>397</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>408</v>
+        <v>397</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6882,7 +6913,7 @@
         <v>82</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>84</v>
@@ -6894,19 +6925,19 @@
         <v>84</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>183</v>
+        <v>398</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>409</v>
+        <v>399</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>411</v>
+        <v>401</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>412</v>
+        <v>402</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>84</v>
@@ -6931,13 +6962,13 @@
         <v>84</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>401</v>
+        <v>84</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>413</v>
+        <v>84</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>414</v>
+        <v>84</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>84</v>
@@ -6955,13 +6986,13 @@
         <v>84</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>408</v>
+        <v>397</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>84</v>
@@ -6982,10 +7013,10 @@
         <v>84</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>415</v>
+        <v>403</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>416</v>
+        <v>404</v>
       </c>
       <c r="AQ39" t="s" s="2">
         <v>84</v>
@@ -6996,10 +7027,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>417</v>
+        <v>405</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>417</v>
+        <v>405</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7022,16 +7053,16 @@
         <v>84</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>418</v>
+        <v>183</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>419</v>
+        <v>406</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>420</v>
+        <v>407</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>421</v>
+        <v>408</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -7057,13 +7088,13 @@
         <v>84</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>84</v>
+        <v>409</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>84</v>
+        <v>410</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>84</v>
+        <v>411</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>84</v>
@@ -7081,7 +7112,7 @@
         <v>84</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>417</v>
+        <v>405</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>82</v>
@@ -7105,27 +7136,27 @@
         <v>84</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>422</v>
+        <v>412</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>423</v>
+        <v>413</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>424</v>
+        <v>414</v>
       </c>
       <c r="AQ40" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR40" t="s" s="2">
-        <v>425</v>
+        <v>415</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>426</v>
+        <v>416</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>426</v>
+        <v>416</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7148,18 +7179,20 @@
         <v>84</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>427</v>
+        <v>183</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>428</v>
+        <v>417</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>429</v>
+        <v>418</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="O41" s="2"/>
+        <v>419</v>
+      </c>
+      <c r="O41" t="s" s="2">
+        <v>420</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>84</v>
       </c>
@@ -7183,13 +7216,13 @@
         <v>84</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>84</v>
+        <v>409</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>84</v>
+        <v>421</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>84</v>
+        <v>422</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>84</v>
@@ -7207,7 +7240,7 @@
         <v>84</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>426</v>
+        <v>416</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
@@ -7231,27 +7264,27 @@
         <v>84</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>431</v>
+        <v>84</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>432</v>
+        <v>423</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="AQ41" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR41" t="s" s="2">
-        <v>434</v>
+        <v>84</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>435</v>
+        <v>425</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>435</v>
+        <v>425</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7262,7 +7295,7 @@
         <v>82</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>84</v>
@@ -7274,20 +7307,18 @@
         <v>84</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>436</v>
+        <v>426</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>437</v>
+        <v>427</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>438</v>
+        <v>428</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>440</v>
-      </c>
+        <v>429</v>
+      </c>
+      <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>84</v>
       </c>
@@ -7335,19 +7366,19 @@
         <v>84</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>435</v>
+        <v>425</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>441</v>
+        <v>106</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>84</v>
@@ -7359,27 +7390,27 @@
         <v>84</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>84</v>
+        <v>430</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>442</v>
+        <v>431</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>443</v>
+        <v>432</v>
       </c>
       <c r="AQ42" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR42" t="s" s="2">
-        <v>84</v>
+        <v>433</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>444</v>
+        <v>434</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>444</v>
+        <v>434</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7402,15 +7433,17 @@
         <v>84</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>161</v>
+        <v>435</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>162</v>
+        <v>436</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N43" s="2"/>
+        <v>437</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>438</v>
+      </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>84</v>
@@ -7459,7 +7492,7 @@
         <v>84</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>164</v>
+        <v>434</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>82</v>
@@ -7471,7 +7504,7 @@
         <v>84</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>84</v>
@@ -7483,31 +7516,31 @@
         <v>84</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>84</v>
+        <v>439</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>84</v>
+        <v>440</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>165</v>
+        <v>441</v>
       </c>
       <c r="AQ43" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR43" t="s" s="2">
-        <v>84</v>
+        <v>442</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>139</v>
+        <v>84</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -7526,18 +7559,20 @@
         <v>84</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>140</v>
+        <v>444</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>141</v>
+        <v>445</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>167</v>
+        <v>446</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O44" s="2"/>
+        <v>447</v>
+      </c>
+      <c r="O44" t="s" s="2">
+        <v>448</v>
+      </c>
       <c r="P44" t="s" s="2">
         <v>84</v>
       </c>
@@ -7585,7 +7620,7 @@
         <v>84</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>171</v>
+        <v>443</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>82</v>
@@ -7597,7 +7632,7 @@
         <v>84</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>145</v>
+        <v>449</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>84</v>
@@ -7612,10 +7647,10 @@
         <v>84</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>84</v>
+        <v>450</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>165</v>
+        <v>451</v>
       </c>
       <c r="AQ44" t="s" s="2">
         <v>84</v>
@@ -7626,46 +7661,42 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>447</v>
+        <v>84</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>84</v>
       </c>
       <c r="I45" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>140</v>
+        <v>161</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>448</v>
+        <v>162</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>149</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="N45" s="2"/>
+      <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>84</v>
       </c>
@@ -7713,19 +7744,19 @@
         <v>84</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>450</v>
+        <v>164</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>145</v>
+        <v>84</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>84</v>
@@ -7743,7 +7774,7 @@
         <v>84</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>137</v>
+        <v>165</v>
       </c>
       <c r="AQ45" t="s" s="2">
         <v>84</v>
@@ -7754,21 +7785,21 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>84</v>
+        <v>139</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>84</v>
@@ -7780,15 +7811,17 @@
         <v>84</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>452</v>
+        <v>140</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>453</v>
+        <v>141</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="N46" s="2"/>
+        <v>167</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>143</v>
+      </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>84</v>
@@ -7837,19 +7870,19 @@
         <v>84</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>451</v>
+        <v>171</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>455</v>
+        <v>84</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>84</v>
@@ -7864,10 +7897,10 @@
         <v>84</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>456</v>
+        <v>84</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>457</v>
+        <v>165</v>
       </c>
       <c r="AQ46" t="s" s="2">
         <v>84</v>
@@ -7878,42 +7911,46 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>84</v>
+        <v>455</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>84</v>
       </c>
       <c r="I47" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>452</v>
+        <v>140</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="N47" s="2"/>
-      <c r="O47" s="2"/>
+        <v>457</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="O47" t="s" s="2">
+        <v>149</v>
+      </c>
       <c r="P47" t="s" s="2">
         <v>84</v>
       </c>
@@ -7967,13 +8004,13 @@
         <v>82</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>455</v>
+        <v>84</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>84</v>
@@ -7988,10 +8025,10 @@
         <v>84</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>456</v>
+        <v>84</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>461</v>
+        <v>137</v>
       </c>
       <c r="AQ47" t="s" s="2">
         <v>84</v>
@@ -8002,10 +8039,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8028,20 +8065,16 @@
         <v>84</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>183</v>
+        <v>460</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>466</v>
-      </c>
+        <v>462</v>
+      </c>
+      <c r="N48" s="2"/>
+      <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>84</v>
       </c>
@@ -8065,13 +8098,13 @@
         <v>84</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>118</v>
+        <v>84</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>467</v>
+        <v>84</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>468</v>
+        <v>84</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>84</v>
@@ -8089,7 +8122,7 @@
         <v>84</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -8098,7 +8131,7 @@
         <v>94</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>84</v>
+        <v>463</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>106</v>
@@ -8113,13 +8146,13 @@
         <v>84</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>469</v>
+        <v>84</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>387</v>
+        <v>465</v>
       </c>
       <c r="AQ48" t="s" s="2">
         <v>84</v>
@@ -8130,10 +8163,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8144,7 +8177,7 @@
         <v>82</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>84</v>
@@ -8156,20 +8189,16 @@
         <v>84</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>183</v>
+        <v>460</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>475</v>
-      </c>
+        <v>468</v>
+      </c>
+      <c r="N49" s="2"/>
+      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>84</v>
       </c>
@@ -8193,13 +8222,13 @@
         <v>84</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>401</v>
+        <v>84</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>476</v>
+        <v>84</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>477</v>
+        <v>84</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>84</v>
@@ -8217,16 +8246,16 @@
         <v>84</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>84</v>
+        <v>463</v>
       </c>
       <c r="AJ49" t="s" s="2">
         <v>106</v>
@@ -8241,13 +8270,13 @@
         <v>84</v>
       </c>
       <c r="AN49" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO49" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="AP49" t="s" s="2">
         <v>469</v>
-      </c>
-      <c r="AO49" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="AP49" t="s" s="2">
-        <v>387</v>
       </c>
       <c r="AQ49" t="s" s="2">
         <v>84</v>
@@ -8258,10 +8287,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>478</v>
+        <v>470</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>478</v>
+        <v>470</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8284,17 +8313,19 @@
         <v>84</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>479</v>
+        <v>183</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>480</v>
+        <v>471</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="N50" s="2"/>
+        <v>472</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>473</v>
+      </c>
       <c r="O50" t="s" s="2">
-        <v>482</v>
+        <v>474</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>84</v>
@@ -8319,13 +8350,13 @@
         <v>84</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>84</v>
+        <v>118</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>84</v>
+        <v>475</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>84</v>
+        <v>476</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>84</v>
@@ -8343,7 +8374,7 @@
         <v>84</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>478</v>
+        <v>470</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
@@ -8367,13 +8398,13 @@
         <v>84</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>84</v>
+        <v>477</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>84</v>
+        <v>478</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>483</v>
+        <v>395</v>
       </c>
       <c r="AQ50" t="s" s="2">
         <v>84</v>
@@ -8384,10 +8415,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8398,7 +8429,7 @@
         <v>82</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>84</v>
@@ -8410,16 +8441,20 @@
         <v>84</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>161</v>
+        <v>183</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="N51" s="2"/>
-      <c r="O51" s="2"/>
+        <v>481</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="O51" t="s" s="2">
+        <v>483</v>
+      </c>
       <c r="P51" t="s" s="2">
         <v>84</v>
       </c>
@@ -8443,13 +8478,13 @@
         <v>84</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>84</v>
+        <v>409</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>84</v>
+        <v>484</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>84</v>
+        <v>485</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>84</v>
@@ -8467,13 +8502,13 @@
         <v>84</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>84</v>
@@ -8491,13 +8526,13 @@
         <v>84</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>84</v>
+        <v>477</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>456</v>
+        <v>478</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>487</v>
+        <v>395</v>
       </c>
       <c r="AQ51" t="s" s="2">
         <v>84</v>
@@ -8508,10 +8543,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8522,7 +8557,7 @@
         <v>82</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>84</v>
@@ -8531,21 +8566,21 @@
         <v>84</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K52" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="L52" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>489</v>
       </c>
-      <c r="L52" t="s" s="2">
+      <c r="N52" s="2"/>
+      <c r="O52" t="s" s="2">
         <v>490</v>
       </c>
-      <c r="M52" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>84</v>
       </c>
@@ -8593,13 +8628,13 @@
         <v>84</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>84</v>
@@ -8620,10 +8655,10 @@
         <v>84</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>493</v>
+        <v>84</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="AQ52" t="s" s="2">
         <v>84</v>
@@ -8634,10 +8669,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8648,7 +8683,7 @@
         <v>82</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>84</v>
@@ -8657,20 +8692,18 @@
         <v>84</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>496</v>
+        <v>161</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>498</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>499</v>
-      </c>
+        <v>494</v>
+      </c>
+      <c r="N53" s="2"/>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>84</v>
@@ -8719,13 +8752,13 @@
         <v>84</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>84</v>
@@ -8746,10 +8779,10 @@
         <v>84</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>493</v>
+        <v>464</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="AQ53" t="s" s="2">
         <v>84</v>
@@ -8760,10 +8793,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8786,20 +8819,18 @@
         <v>95</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>436</v>
+        <v>497</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>504</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>505</v>
-      </c>
+        <v>500</v>
+      </c>
+      <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>84</v>
       </c>
@@ -8847,7 +8878,7 @@
         <v>84</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>82</v>
@@ -8874,10 +8905,10 @@
         <v>84</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>506</v>
+        <v>501</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="AQ54" t="s" s="2">
         <v>84</v>
@@ -8888,10 +8919,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>508</v>
+        <v>503</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>508</v>
+        <v>503</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8902,7 +8933,7 @@
         <v>82</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>84</v>
@@ -8911,18 +8942,20 @@
         <v>84</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>161</v>
+        <v>504</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>162</v>
+        <v>505</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N55" s="2"/>
+        <v>506</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>507</v>
+      </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>84</v>
@@ -8971,19 +9004,19 @@
         <v>84</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>164</v>
+        <v>503</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>84</v>
@@ -8998,10 +9031,10 @@
         <v>84</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>84</v>
+        <v>501</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>165</v>
+        <v>508</v>
       </c>
       <c r="AQ55" t="s" s="2">
         <v>84</v>
@@ -9019,7 +9052,7 @@
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>139</v>
+        <v>84</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -9035,21 +9068,23 @@
         <v>84</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>140</v>
+        <v>444</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>141</v>
+        <v>510</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>167</v>
+        <v>511</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O56" s="2"/>
+        <v>512</v>
+      </c>
+      <c r="O56" t="s" s="2">
+        <v>513</v>
+      </c>
       <c r="P56" t="s" s="2">
         <v>84</v>
       </c>
@@ -9097,7 +9132,7 @@
         <v>84</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>171</v>
+        <v>509</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>82</v>
@@ -9109,7 +9144,7 @@
         <v>84</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>84</v>
@@ -9124,10 +9159,10 @@
         <v>84</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>84</v>
+        <v>514</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>165</v>
+        <v>515</v>
       </c>
       <c r="AQ56" t="s" s="2">
         <v>84</v>
@@ -9138,46 +9173,42 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>510</v>
+        <v>516</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>510</v>
+        <v>516</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>447</v>
+        <v>84</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>84</v>
       </c>
       <c r="I57" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>140</v>
+        <v>161</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>448</v>
+        <v>162</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O57" t="s" s="2">
-        <v>149</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="N57" s="2"/>
+      <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>84</v>
       </c>
@@ -9225,19 +9256,19 @@
         <v>84</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>450</v>
+        <v>164</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>145</v>
+        <v>84</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>84</v>
@@ -9255,7 +9286,7 @@
         <v>84</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>137</v>
+        <v>165</v>
       </c>
       <c r="AQ57" t="s" s="2">
         <v>84</v>
@@ -9266,21 +9297,21 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>84</v>
+        <v>139</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>84</v>
@@ -9289,23 +9320,21 @@
         <v>84</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>183</v>
+        <v>140</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>512</v>
+        <v>141</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>513</v>
+        <v>167</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>514</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>277</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>84</v>
       </c>
@@ -9329,13 +9358,13 @@
         <v>84</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>401</v>
+        <v>84</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>515</v>
+        <v>84</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>516</v>
+        <v>84</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>84</v>
@@ -9353,19 +9382,19 @@
         <v>84</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>511</v>
+        <v>171</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>84</v>
@@ -9377,16 +9406,16 @@
         <v>84</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>517</v>
+        <v>84</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>281</v>
+        <v>84</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>282</v>
+        <v>165</v>
       </c>
       <c r="AQ58" t="s" s="2">
-        <v>283</v>
+        <v>84</v>
       </c>
       <c r="AR58" t="s" s="2">
         <v>84</v>
@@ -9401,38 +9430,38 @@
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>84</v>
+        <v>455</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>84</v>
       </c>
       <c r="I59" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="J59" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>353</v>
+        <v>140</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>519</v>
+        <v>456</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>355</v>
+        <v>457</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>520</v>
+        <v>143</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>357</v>
+        <v>149</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>84</v>
@@ -9481,19 +9510,19 @@
         <v>84</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>518</v>
+        <v>458</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>84</v>
@@ -9505,27 +9534,27 @@
         <v>84</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>521</v>
+        <v>84</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>361</v>
+        <v>84</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>362</v>
+        <v>137</v>
       </c>
       <c r="AQ59" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR59" t="s" s="2">
-        <v>363</v>
+        <v>84</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9533,7 +9562,7 @@
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G60" t="s" s="2">
         <v>94</v>
@@ -9545,22 +9574,22 @@
         <v>84</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K60" t="s" s="2">
         <v>183</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>372</v>
+        <v>277</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>84</v>
@@ -9585,13 +9614,13 @@
         <v>84</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>188</v>
+        <v>409</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>373</v>
+        <v>523</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>374</v>
+        <v>524</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>84</v>
@@ -9609,16 +9638,16 @@
         <v>84</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="AG60" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AH60" t="s" s="2">
         <v>94</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>526</v>
+        <v>84</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>106</v>
@@ -9633,16 +9662,16 @@
         <v>84</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>84</v>
+        <v>525</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>137</v>
+        <v>281</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>376</v>
+        <v>282</v>
       </c>
       <c r="AQ60" t="s" s="2">
-        <v>84</v>
+        <v>283</v>
       </c>
       <c r="AR60" t="s" s="2">
         <v>84</v>
@@ -9650,21 +9679,21 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>378</v>
+        <v>84</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>84</v>
@@ -9673,22 +9702,22 @@
         <v>84</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>183</v>
+        <v>353</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>379</v>
+        <v>527</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>380</v>
+        <v>355</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>381</v>
+        <v>528</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>382</v>
+        <v>357</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>84</v>
@@ -9713,13 +9742,13 @@
         <v>84</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>188</v>
+        <v>84</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>383</v>
+        <v>84</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>384</v>
+        <v>84</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>84</v>
@@ -9737,13 +9766,13 @@
         <v>84</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>84</v>
@@ -9761,27 +9790,27 @@
         <v>84</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>385</v>
+        <v>529</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>386</v>
+        <v>361</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>387</v>
+        <v>362</v>
       </c>
       <c r="AQ61" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR61" t="s" s="2">
-        <v>388</v>
+        <v>363</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9792,7 +9821,7 @@
         <v>82</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>84</v>
@@ -9804,19 +9833,19 @@
         <v>84</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>85</v>
+        <v>183</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>439</v>
+        <v>533</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>440</v>
+        <v>379</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>84</v>
@@ -9841,13 +9870,13 @@
         <v>84</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>84</v>
+        <v>188</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>84</v>
+        <v>380</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>84</v>
+        <v>381</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>84</v>
@@ -9865,16 +9894,16 @@
         <v>84</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>84</v>
+        <v>534</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>106</v>
@@ -9892,20 +9921,276 @@
         <v>84</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>442</v>
+        <v>137</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>443</v>
+        <v>384</v>
       </c>
       <c r="AQ62" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR62" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="63" hidden="true">
+      <c r="A63" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="C63" s="2"/>
+      <c r="D63" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="E63" s="2"/>
+      <c r="F63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H63" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I63" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J63" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K63" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="L63" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="O63" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="P63" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q63" s="2"/>
+      <c r="R63" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S63" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T63" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U63" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V63" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W63" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X63" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="Z63" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF63" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="AG63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI63" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK63" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL63" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM63" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN63" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="AO63" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="AP63" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="AQ63" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR63" t="s" s="2">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="64" hidden="true">
+      <c r="A64" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="C64" s="2"/>
+      <c r="D64" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E64" s="2"/>
+      <c r="F64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H64" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I64" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J64" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K64" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="O64" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="P64" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q64" s="2"/>
+      <c r="R64" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S64" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T64" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U64" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V64" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W64" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X64" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z64" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA64" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB64" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD64" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE64" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF64" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="AG64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI64" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ64" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK64" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN64" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO64" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="AP64" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="AQ64" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR64" t="s" s="2">
         <v>84</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AR62">
+  <autoFilter ref="A1:AR64">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -9915,7 +10200,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI61">
+  <conditionalFormatting sqref="A2:AI63">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T07:33:38+00:00</t>
+    <t>2024-04-03T08:58:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T08:58:56+00:00</t>
+    <t>2024-04-10T18:17:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file RAD/NUC MED REPORTS (#74) to us-core-observation-imaging</t>
+    <t>This StructureDefinition contains the maps for VistA file RAD/NUC MED REPORTS (74) to us-core-observation-imaging</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -662,7 +662,7 @@
     <t>Identifier.value</t>
   </si>
   <si>
-    <t>1619: source value from RAD/NUC MED REPORTS - IEN (#74-.001)</t>
+    <t>1619: source value from RAD/NUC MED REPORTS - IEN (74-.001)</t>
   </si>
   <si>
     <t>CX.1 / EI.1</t>
@@ -767,7 +767,7 @@
     <t>To link an Observation to an Encounter use `encounter`.  See the  [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below for guidance on referencing another Observation.</t>
   </si>
   <si>
-    <t>1620: reference from REGISTERED EXAMS - EXAMINATIONS (#70.02-50)</t>
+    <t>1620: reference from REGISTERED EXAMS - EXAMINATIONS (70.02-50)</t>
   </si>
   <si>
     <t>Event.partOf</t>
@@ -797,7 +797,7 @@
     <t>http://va.gov/fhir/ValueSet/VSVFImageStatusRadNuc</t>
   </si>
   <si>
-    <t>1623: terminologyMaps using VF_ImageStatusRadNuc on RAD/NUC MED REPORTS - REPORT STATUS (#74-5)</t>
+    <t>1623: terminologyMaps using VF_ImageStatusRadNuc on RAD/NUC MED REPORTS - REPORT STATUS (74-5)</t>
   </si>
   <si>
     <t>SStaff.RadiologyNuclearMedicineReport.ReportStatus</t>
@@ -925,7 +925,7 @@
     <t>Observations have no value if you don't know who or what they're about.</t>
   </si>
   <si>
-    <t>1633: reference from RAD/NUC MED REPORTS - PATIENT NAME (#74-2)</t>
+    <t>1633: reference from RAD/NUC MED REPORTS - PATIENT NAME (74-2)</t>
   </si>
   <si>
     <t>Event.subject</t>
@@ -1051,7 +1051,7 @@
 </t>
   </si>
   <si>
-    <t>1636: source value from RAD/NUC MED REPORTS - EXAM DATE/TIME (#74-3)</t>
+    <t>1636: source value from RAD/NUC MED REPORTS - EXAM DATE/TIME (74-3)</t>
   </si>
   <si>
     <t>SStaff.RadiologyNuclearMedicineReport.ExamDateTime</t>
@@ -1073,7 +1073,7 @@
     <t>For Observations that don’t require review and verification, it may be the same as the [`lastUpdated` ](http://hl7.org/fhir/R4/resource-definitions.html#Meta.lastUpdated) time of the resource itself.  For Observations that do require review and verification for certain updates, it might not be the same as the `lastUpdated` time of the resource itself due to a non-clinically significant update that doesn’t require the new version to be reviewed and verified again.</t>
   </si>
   <si>
-    <t>1639: source value from RAD/NUC MED REPORTS - VERIFIED DATE (#74-7)</t>
+    <t>1639: source value from RAD/NUC MED REPORTS - VERIFIED DATE (74-7)</t>
   </si>
   <si>
     <t>SStaff.RadiologyNuclearMedicineReport.VerifiedDateTime</t>
@@ -1104,7 +1104,7 @@
     <t>May give a degree of confidence in the observation and also indicates where follow-up questions should be directed.</t>
   </si>
   <si>
-    <t>1642: source value from RAD/NUC MED REPORTS - VERIFYING PHYSICIAN (#74-9)</t>
+    <t>1642: source value from RAD/NUC MED REPORTS - VERIFYING PHYSICIAN (74-9)</t>
   </si>
   <si>
     <t>Event.performer.actor</t>
@@ -1164,7 +1164,7 @@
     <t>valueString</t>
   </si>
   <si>
-    <t>1647: source value from RAD/NUC MED REPORTS - IMPRESSION TEXT &gt; IMPRESSION TEXT - IMPRESSION TEXT (#74-300 &gt; 74.03-.01)</t>
+    <t>1647: source value from RAD/NUC MED REPORTS - IMPRESSION TEXT &gt; IMPRESSION TEXT - IMPRESSION TEXT (74-300 &gt; 74.03-.01)</t>
   </si>
   <si>
     <t>SPatientText.RadiologyImpressions.ImpressionText</t>
@@ -2061,7 +2061,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="124.171875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="122.63671875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="54.1640625" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="247.40625" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.36.0</t>
+    <t>0.37.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T18:17:58+00:00</t>
+    <t>2024-04-10T21:21:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.37.0</t>
+    <t>0.38.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T21:21:54+00:00</t>
+    <t>2024-04-12T10:04:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>VA (https://www.va.gov)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.38.0</t>
+    <t>0.39.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T10:04:01+00:00</t>
+    <t>2024-04-12T16:57:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.39.0</t>
+    <t>0.40.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T16:57:46+00:00</t>
+    <t>2024-04-13T07:20:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.40.0</t>
+    <t>0.41.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-13T07:20:06+00:00</t>
+    <t>2024-04-21T15:38:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.41.0</t>
+    <t>0.42.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-21T15:38:45+00:00</t>
+    <t>2024-04-22T07:04:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.42.0</t>
+    <t>0.43.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-22T07:04:34+00:00</t>
+    <t>2024-04-24T08:47:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.43.0</t>
+    <t>0.44.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-24T08:47:54+00:00</t>
+    <t>2024-04-25T08:17:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2624" uniqueCount="539">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2624" uniqueCount="538">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.44.0</t>
+    <t>0.45.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-25T08:17:47+00:00</t>
+    <t>2024-05-01T09:37:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1164,10 +1164,7 @@
     <t>valueString</t>
   </si>
   <si>
-    <t>1647: source value from RAD/NUC MED REPORTS - IMPRESSION TEXT &gt; IMPRESSION TEXT - IMPRESSION TEXT (74-300 &gt; 74.03-.01)</t>
-  </si>
-  <si>
-    <t>SPatientText.RadiologyImpressions.ImpressionText</t>
+    <t>1647: source value from RAD/NUC MED REPORTS - IMPRESSION TEXT (74-300)</t>
   </si>
   <si>
     <t>Observation.value[x]:valueQuantity</t>
@@ -2061,7 +2058,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="122.63671875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="99.80078125" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="54.1640625" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="247.40625" customWidth="true" bestFit="true"/>
@@ -6360,7 +6357,7 @@
         <v>366</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>367</v>
+        <v>84</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>84</v>
@@ -6383,13 +6380,13 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B35" t="s" s="2">
         <v>352</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="D35" t="s" s="2">
         <v>84</v>
@@ -6411,7 +6408,7 @@
         <v>95</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="L35" t="s" s="2">
         <v>354</v>
@@ -6487,7 +6484,7 @@
         <v>359</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>84</v>
@@ -6513,13 +6510,13 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B36" t="s" s="2">
         <v>352</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D36" t="s" s="2">
         <v>84</v>
@@ -6617,7 +6614,7 @@
         <v>359</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>84</v>
@@ -6643,10 +6640,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6672,16 +6669,16 @@
         <v>183</v>
       </c>
       <c r="L37" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>376</v>
       </c>
-      <c r="M37" t="s" s="2">
+      <c r="N37" t="s" s="2">
         <v>377</v>
       </c>
-      <c r="N37" t="s" s="2">
+      <c r="O37" t="s" s="2">
         <v>378</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>379</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>84</v>
@@ -6709,11 +6706,11 @@
         <v>188</v>
       </c>
       <c r="Y37" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="Z37" t="s" s="2">
         <v>380</v>
       </c>
-      <c r="Z37" t="s" s="2">
-        <v>381</v>
-      </c>
       <c r="AA37" t="s" s="2">
         <v>84</v>
       </c>
@@ -6730,7 +6727,7 @@
         <v>84</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>82</v>
@@ -6739,13 +6736,13 @@
         <v>94</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>84</v>
@@ -6760,7 +6757,7 @@
         <v>137</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="AQ37" t="s" s="2">
         <v>84</v>
@@ -6771,14 +6768,14 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -6800,16 +6797,16 @@
         <v>183</v>
       </c>
       <c r="L38" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="M38" t="s" s="2">
+      <c r="N38" t="s" s="2">
         <v>388</v>
       </c>
-      <c r="N38" t="s" s="2">
+      <c r="O38" t="s" s="2">
         <v>389</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>390</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>84</v>
@@ -6837,11 +6834,11 @@
         <v>188</v>
       </c>
       <c r="Y38" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="Z38" t="s" s="2">
         <v>391</v>
       </c>
-      <c r="Z38" t="s" s="2">
-        <v>392</v>
-      </c>
       <c r="AA38" t="s" s="2">
         <v>84</v>
       </c>
@@ -6858,7 +6855,7 @@
         <v>84</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>82</v>
@@ -6882,27 +6879,27 @@
         <v>84</v>
       </c>
       <c r="AN38" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="AO38" t="s" s="2">
         <v>393</v>
       </c>
-      <c r="AO38" t="s" s="2">
+      <c r="AP38" t="s" s="2">
         <v>394</v>
       </c>
-      <c r="AP38" t="s" s="2">
+      <c r="AQ38" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR38" t="s" s="2">
         <v>395</v>
-      </c>
-      <c r="AQ38" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR38" t="s" s="2">
-        <v>396</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6925,19 +6922,19 @@
         <v>84</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="L39" t="s" s="2">
         <v>398</v>
       </c>
-      <c r="L39" t="s" s="2">
+      <c r="M39" t="s" s="2">
         <v>399</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="N39" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="N39" t="s" s="2">
+      <c r="O39" t="s" s="2">
         <v>401</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>402</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>84</v>
@@ -6986,7 +6983,7 @@
         <v>84</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
@@ -7013,10 +7010,10 @@
         <v>84</v>
       </c>
       <c r="AO39" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="AP39" t="s" s="2">
         <v>403</v>
-      </c>
-      <c r="AP39" t="s" s="2">
-        <v>404</v>
       </c>
       <c r="AQ39" t="s" s="2">
         <v>84</v>
@@ -7027,10 +7024,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7056,13 +7053,13 @@
         <v>183</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>406</v>
       </c>
-      <c r="M40" t="s" s="2">
+      <c r="N40" t="s" s="2">
         <v>407</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>408</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -7088,14 +7085,14 @@
         <v>84</v>
       </c>
       <c r="X40" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="Y40" t="s" s="2">
         <v>409</v>
       </c>
-      <c r="Y40" t="s" s="2">
+      <c r="Z40" t="s" s="2">
         <v>410</v>
       </c>
-      <c r="Z40" t="s" s="2">
-        <v>411</v>
-      </c>
       <c r="AA40" t="s" s="2">
         <v>84</v>
       </c>
@@ -7112,7 +7109,7 @@
         <v>84</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>82</v>
@@ -7136,27 +7133,27 @@
         <v>84</v>
       </c>
       <c r="AN40" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="AO40" t="s" s="2">
         <v>412</v>
       </c>
-      <c r="AO40" t="s" s="2">
+      <c r="AP40" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="AP40" t="s" s="2">
+      <c r="AQ40" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR40" t="s" s="2">
         <v>414</v>
-      </c>
-      <c r="AQ40" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR40" t="s" s="2">
-        <v>415</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7182,16 +7179,16 @@
         <v>183</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>417</v>
       </c>
-      <c r="M41" t="s" s="2">
+      <c r="N41" t="s" s="2">
         <v>418</v>
       </c>
-      <c r="N41" t="s" s="2">
+      <c r="O41" t="s" s="2">
         <v>419</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>420</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>84</v>
@@ -7216,14 +7213,14 @@
         <v>84</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="Y41" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="Z41" t="s" s="2">
         <v>421</v>
       </c>
-      <c r="Z41" t="s" s="2">
-        <v>422</v>
-      </c>
       <c r="AA41" t="s" s="2">
         <v>84</v>
       </c>
@@ -7240,7 +7237,7 @@
         <v>84</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
@@ -7267,10 +7264,10 @@
         <v>84</v>
       </c>
       <c r="AO41" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="AP41" t="s" s="2">
         <v>423</v>
-      </c>
-      <c r="AP41" t="s" s="2">
-        <v>424</v>
       </c>
       <c r="AQ41" t="s" s="2">
         <v>84</v>
@@ -7281,10 +7278,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7307,16 +7304,16 @@
         <v>84</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="L42" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="M42" t="s" s="2">
         <v>427</v>
       </c>
-      <c r="M42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>428</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>429</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7366,7 +7363,7 @@
         <v>84</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>82</v>
@@ -7390,27 +7387,27 @@
         <v>84</v>
       </c>
       <c r="AN42" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="AO42" t="s" s="2">
         <v>430</v>
       </c>
-      <c r="AO42" t="s" s="2">
+      <c r="AP42" t="s" s="2">
         <v>431</v>
       </c>
-      <c r="AP42" t="s" s="2">
+      <c r="AQ42" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR42" t="s" s="2">
         <v>432</v>
-      </c>
-      <c r="AQ42" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR42" t="s" s="2">
-        <v>433</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7433,16 +7430,16 @@
         <v>84</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="L43" t="s" s="2">
         <v>435</v>
       </c>
-      <c r="L43" t="s" s="2">
+      <c r="M43" t="s" s="2">
         <v>436</v>
       </c>
-      <c r="M43" t="s" s="2">
+      <c r="N43" t="s" s="2">
         <v>437</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>438</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -7492,7 +7489,7 @@
         <v>84</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>82</v>
@@ -7516,27 +7513,27 @@
         <v>84</v>
       </c>
       <c r="AN43" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="AO43" t="s" s="2">
         <v>439</v>
       </c>
-      <c r="AO43" t="s" s="2">
+      <c r="AP43" t="s" s="2">
         <v>440</v>
       </c>
-      <c r="AP43" t="s" s="2">
+      <c r="AQ43" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR43" t="s" s="2">
         <v>441</v>
-      </c>
-      <c r="AQ43" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR43" t="s" s="2">
-        <v>442</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7559,19 +7556,19 @@
         <v>84</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="L44" t="s" s="2">
         <v>444</v>
       </c>
-      <c r="L44" t="s" s="2">
+      <c r="M44" t="s" s="2">
         <v>445</v>
       </c>
-      <c r="M44" t="s" s="2">
+      <c r="N44" t="s" s="2">
         <v>446</v>
       </c>
-      <c r="N44" t="s" s="2">
+      <c r="O44" t="s" s="2">
         <v>447</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>448</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>84</v>
@@ -7620,7 +7617,7 @@
         <v>84</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>82</v>
@@ -7632,25 +7629,25 @@
         <v>84</v>
       </c>
       <c r="AJ44" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="AK44" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL44" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM44" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN44" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO44" t="s" s="2">
         <v>449</v>
       </c>
-      <c r="AK44" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL44" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM44" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN44" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO44" t="s" s="2">
+      <c r="AP44" t="s" s="2">
         <v>450</v>
-      </c>
-      <c r="AP44" t="s" s="2">
-        <v>451</v>
       </c>
       <c r="AQ44" t="s" s="2">
         <v>84</v>
@@ -7661,10 +7658,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7785,10 +7782,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7911,14 +7908,14 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7940,10 +7937,10 @@
         <v>140</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>456</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>457</v>
       </c>
       <c r="N47" t="s" s="2">
         <v>143</v>
@@ -7998,7 +7995,7 @@
         <v>84</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
@@ -8039,10 +8036,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8065,13 +8062,13 @@
         <v>84</v>
       </c>
       <c r="K48" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="L48" t="s" s="2">
         <v>460</v>
       </c>
-      <c r="L48" t="s" s="2">
+      <c r="M48" t="s" s="2">
         <v>461</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>462</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -8122,7 +8119,7 @@
         <v>84</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -8131,7 +8128,7 @@
         <v>94</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>106</v>
@@ -8149,10 +8146,10 @@
         <v>84</v>
       </c>
       <c r="AO48" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="AP48" t="s" s="2">
         <v>464</v>
-      </c>
-      <c r="AP48" t="s" s="2">
-        <v>465</v>
       </c>
       <c r="AQ48" t="s" s="2">
         <v>84</v>
@@ -8163,10 +8160,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8189,13 +8186,13 @@
         <v>84</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="M49" t="s" s="2">
         <v>467</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>468</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -8246,7 +8243,7 @@
         <v>84</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
@@ -8255,7 +8252,7 @@
         <v>94</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="AJ49" t="s" s="2">
         <v>106</v>
@@ -8273,10 +8270,10 @@
         <v>84</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="AQ49" t="s" s="2">
         <v>84</v>
@@ -8287,10 +8284,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8316,16 +8313,16 @@
         <v>183</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>471</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="N50" t="s" s="2">
         <v>472</v>
       </c>
-      <c r="N50" t="s" s="2">
+      <c r="O50" t="s" s="2">
         <v>473</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>474</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>84</v>
@@ -8353,11 +8350,11 @@
         <v>118</v>
       </c>
       <c r="Y50" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="Z50" t="s" s="2">
         <v>475</v>
       </c>
-      <c r="Z50" t="s" s="2">
-        <v>476</v>
-      </c>
       <c r="AA50" t="s" s="2">
         <v>84</v>
       </c>
@@ -8374,7 +8371,7 @@
         <v>84</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
@@ -8398,13 +8395,13 @@
         <v>84</v>
       </c>
       <c r="AN50" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="AO50" t="s" s="2">
         <v>477</v>
       </c>
-      <c r="AO50" t="s" s="2">
-        <v>478</v>
-      </c>
       <c r="AP50" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="AQ50" t="s" s="2">
         <v>84</v>
@@ -8415,10 +8412,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8444,16 +8441,16 @@
         <v>183</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>480</v>
       </c>
-      <c r="M51" t="s" s="2">
+      <c r="N51" t="s" s="2">
         <v>481</v>
       </c>
-      <c r="N51" t="s" s="2">
+      <c r="O51" t="s" s="2">
         <v>482</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>483</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>84</v>
@@ -8478,14 +8475,14 @@
         <v>84</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="Y51" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="Z51" t="s" s="2">
         <v>484</v>
       </c>
-      <c r="Z51" t="s" s="2">
-        <v>485</v>
-      </c>
       <c r="AA51" t="s" s="2">
         <v>84</v>
       </c>
@@ -8502,7 +8499,7 @@
         <v>84</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
@@ -8526,13 +8523,13 @@
         <v>84</v>
       </c>
       <c r="AN51" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="AO51" t="s" s="2">
         <v>477</v>
       </c>
-      <c r="AO51" t="s" s="2">
-        <v>478</v>
-      </c>
       <c r="AP51" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="AQ51" t="s" s="2">
         <v>84</v>
@@ -8543,10 +8540,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8569,17 +8566,17 @@
         <v>84</v>
       </c>
       <c r="K52" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="L52" t="s" s="2">
         <v>487</v>
       </c>
-      <c r="L52" t="s" s="2">
+      <c r="M52" t="s" s="2">
         <v>488</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>489</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>84</v>
@@ -8628,7 +8625,7 @@
         <v>84</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
@@ -8658,7 +8655,7 @@
         <v>84</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="AQ52" t="s" s="2">
         <v>84</v>
@@ -8669,10 +8666,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8698,10 +8695,10 @@
         <v>161</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>493</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>494</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8752,7 +8749,7 @@
         <v>84</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>82</v>
@@ -8779,10 +8776,10 @@
         <v>84</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="AQ53" t="s" s="2">
         <v>84</v>
@@ -8793,10 +8790,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8819,16 +8816,16 @@
         <v>95</v>
       </c>
       <c r="K54" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="L54" t="s" s="2">
         <v>497</v>
       </c>
-      <c r="L54" t="s" s="2">
+      <c r="M54" t="s" s="2">
         <v>498</v>
       </c>
-      <c r="M54" t="s" s="2">
+      <c r="N54" t="s" s="2">
         <v>499</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>500</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8878,7 +8875,7 @@
         <v>84</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>82</v>
@@ -8905,10 +8902,10 @@
         <v>84</v>
       </c>
       <c r="AO54" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="AP54" t="s" s="2">
         <v>501</v>
-      </c>
-      <c r="AP54" t="s" s="2">
-        <v>502</v>
       </c>
       <c r="AQ54" t="s" s="2">
         <v>84</v>
@@ -8919,10 +8916,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8945,16 +8942,16 @@
         <v>95</v>
       </c>
       <c r="K55" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="L55" t="s" s="2">
         <v>504</v>
       </c>
-      <c r="L55" t="s" s="2">
+      <c r="M55" t="s" s="2">
         <v>505</v>
       </c>
-      <c r="M55" t="s" s="2">
+      <c r="N55" t="s" s="2">
         <v>506</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>507</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -9004,7 +9001,7 @@
         <v>84</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>82</v>
@@ -9031,10 +9028,10 @@
         <v>84</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="AQ55" t="s" s="2">
         <v>84</v>
@@ -9045,10 +9042,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9071,19 +9068,19 @@
         <v>95</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="L56" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>510</v>
       </c>
-      <c r="M56" t="s" s="2">
+      <c r="N56" t="s" s="2">
         <v>511</v>
       </c>
-      <c r="N56" t="s" s="2">
+      <c r="O56" t="s" s="2">
         <v>512</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>513</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>84</v>
@@ -9132,7 +9129,7 @@
         <v>84</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>82</v>
@@ -9159,10 +9156,10 @@
         <v>84</v>
       </c>
       <c r="AO56" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="AP56" t="s" s="2">
         <v>514</v>
-      </c>
-      <c r="AP56" t="s" s="2">
-        <v>515</v>
       </c>
       <c r="AQ56" t="s" s="2">
         <v>84</v>
@@ -9173,10 +9170,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9297,10 +9294,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9423,14 +9420,14 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -9452,10 +9449,10 @@
         <v>140</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>456</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>457</v>
       </c>
       <c r="N59" t="s" s="2">
         <v>143</v>
@@ -9510,7 +9507,7 @@
         <v>84</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
@@ -9551,10 +9548,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9580,13 +9577,13 @@
         <v>183</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="M60" t="s" s="2">
         <v>520</v>
       </c>
-      <c r="M60" t="s" s="2">
+      <c r="N60" t="s" s="2">
         <v>521</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>522</v>
       </c>
       <c r="O60" t="s" s="2">
         <v>277</v>
@@ -9614,14 +9611,14 @@
         <v>84</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="Y60" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="Z60" t="s" s="2">
         <v>523</v>
       </c>
-      <c r="Z60" t="s" s="2">
-        <v>524</v>
-      </c>
       <c r="AA60" t="s" s="2">
         <v>84</v>
       </c>
@@ -9638,7 +9635,7 @@
         <v>84</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>94</v>
@@ -9662,7 +9659,7 @@
         <v>84</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>281</v>
@@ -9679,10 +9676,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9708,13 +9705,13 @@
         <v>353</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="M61" t="s" s="2">
         <v>355</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="O61" t="s" s="2">
         <v>357</v>
@@ -9766,7 +9763,7 @@
         <v>84</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>82</v>
@@ -9790,7 +9787,7 @@
         <v>84</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>361</v>
@@ -9807,10 +9804,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9836,16 +9833,16 @@
         <v>183</v>
       </c>
       <c r="L62" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="M62" t="s" s="2">
         <v>531</v>
       </c>
-      <c r="M62" t="s" s="2">
+      <c r="N62" t="s" s="2">
         <v>532</v>
       </c>
-      <c r="N62" t="s" s="2">
-        <v>533</v>
-      </c>
       <c r="O62" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>84</v>
@@ -9873,11 +9870,11 @@
         <v>188</v>
       </c>
       <c r="Y62" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="Z62" t="s" s="2">
         <v>380</v>
       </c>
-      <c r="Z62" t="s" s="2">
-        <v>381</v>
-      </c>
       <c r="AA62" t="s" s="2">
         <v>84</v>
       </c>
@@ -9894,7 +9891,7 @@
         <v>84</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>82</v>
@@ -9903,7 +9900,7 @@
         <v>94</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>106</v>
@@ -9924,7 +9921,7 @@
         <v>137</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="AQ62" t="s" s="2">
         <v>84</v>
@@ -9935,14 +9932,14 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -9964,16 +9961,16 @@
         <v>183</v>
       </c>
       <c r="L63" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="M63" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="M63" t="s" s="2">
+      <c r="N63" t="s" s="2">
         <v>388</v>
       </c>
-      <c r="N63" t="s" s="2">
+      <c r="O63" t="s" s="2">
         <v>389</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>390</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>84</v>
@@ -10001,11 +9998,11 @@
         <v>188</v>
       </c>
       <c r="Y63" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="Z63" t="s" s="2">
         <v>391</v>
       </c>
-      <c r="Z63" t="s" s="2">
-        <v>392</v>
-      </c>
       <c r="AA63" t="s" s="2">
         <v>84</v>
       </c>
@@ -10022,7 +10019,7 @@
         <v>84</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>82</v>
@@ -10046,27 +10043,27 @@
         <v>84</v>
       </c>
       <c r="AN63" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="AO63" t="s" s="2">
         <v>393</v>
       </c>
-      <c r="AO63" t="s" s="2">
+      <c r="AP63" t="s" s="2">
         <v>394</v>
       </c>
-      <c r="AP63" t="s" s="2">
+      <c r="AQ63" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR63" t="s" s="2">
         <v>395</v>
-      </c>
-      <c r="AQ63" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR63" t="s" s="2">
-        <v>396</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10092,16 +10089,16 @@
         <v>85</v>
       </c>
       <c r="L64" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="M64" t="s" s="2">
         <v>537</v>
       </c>
-      <c r="M64" t="s" s="2">
-        <v>538</v>
-      </c>
       <c r="N64" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="O64" t="s" s="2">
         <v>447</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>448</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>84</v>
@@ -10150,7 +10147,7 @@
         <v>84</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>82</v>
@@ -10177,10 +10174,10 @@
         <v>84</v>
       </c>
       <c r="AO64" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="AP64" t="s" s="2">
         <v>450</v>
-      </c>
-      <c r="AP64" t="s" s="2">
-        <v>451</v>
       </c>
       <c r="AQ64" t="s" s="2">
         <v>84</v>

--- a/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.45.0</t>
+    <t>0.46.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T09:37:14+00:00</t>
+    <t>2024-05-01T10:34:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2624" uniqueCount="538">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2624" uniqueCount="540">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.46.0</t>
+    <t>0.47.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T10:34:27+00:00</t>
+    <t>2024-05-04T09:18:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -928,6 +928,9 @@
     <t>1633: reference from RAD/NUC MED REPORTS - PATIENT NAME (74-2)</t>
   </si>
   <si>
+    <t>SStaff.RadiologyNuclearMedicineReport.PatientIEN</t>
+  </si>
+  <si>
     <t>Event.subject</t>
   </si>
   <si>
@@ -1105,6 +1108,9 @@
   </si>
   <si>
     <t>1642: source value from RAD/NUC MED REPORTS - VERIFYING PHYSICIAN (74-9)</t>
+  </si>
+  <si>
+    <t>SStaff.RadiologyNuclearMedicineReport.VerifyingPhysicianStaffIEN</t>
   </si>
   <si>
     <t>Event.performer.actor</t>
@@ -2059,7 +2065,7 @@
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="99.80078125" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="54.1640625" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="62.34375" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="247.40625" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="255.0" customWidth="true" bestFit="true"/>
@@ -5339,22 +5345,22 @@
         <v>291</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>84</v>
+        <v>292</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AQ26" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AR26" t="s" s="2">
         <v>84</v>
@@ -5362,10 +5368,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5388,16 +5394,16 @@
         <v>95</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -5447,7 +5453,7 @@
         <v>84</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>82</v>
@@ -5477,10 +5483,10 @@
         <v>281</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AQ27" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AR27" t="s" s="2">
         <v>84</v>
@@ -5488,14 +5494,14 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -5514,19 +5520,19 @@
         <v>95</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>84</v>
@@ -5575,7 +5581,7 @@
         <v>84</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>82</v>
@@ -5596,19 +5602,19 @@
         <v>84</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AQ28" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AR28" t="s" s="2">
         <v>84</v>
@@ -5616,14 +5622,14 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -5642,19 +5648,19 @@
         <v>95</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>84</v>
@@ -5691,7 +5697,7 @@
         <v>84</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AC29" s="2"/>
       <c r="AD29" t="s" s="2">
@@ -5701,7 +5707,7 @@
         <v>170</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>82</v>
@@ -5710,10 +5716,10 @@
         <v>94</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>84</v>
@@ -5722,19 +5728,19 @@
         <v>84</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AQ29" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AR29" t="s" s="2">
         <v>84</v>
@@ -5742,16 +5748,16 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D30" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -5770,19 +5776,19 @@
         <v>95</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>84</v>
@@ -5831,7 +5837,7 @@
         <v>84</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>82</v>
@@ -5840,31 +5846,31 @@
         <v>94</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AQ30" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AR30" t="s" s="2">
         <v>84</v>
@@ -5872,10 +5878,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5898,16 +5904,16 @@
         <v>95</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5957,7 +5963,7 @@
         <v>84</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>82</v>
@@ -5972,10 +5978,10 @@
         <v>106</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>84</v>
@@ -5984,13 +5990,13 @@
         <v>84</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AQ31" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AR31" t="s" s="2">
         <v>84</v>
@@ -5998,10 +6004,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6024,17 +6030,17 @@
         <v>95</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>84</v>
@@ -6083,7 +6089,7 @@
         <v>84</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>82</v>
@@ -6098,25 +6104,25 @@
         <v>106</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>84</v>
+        <v>349</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="AQ32" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="AR32" t="s" s="2">
         <v>84</v>
@@ -6124,10 +6130,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6150,19 +6156,19 @@
         <v>95</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>84</v>
@@ -6199,7 +6205,7 @@
         <v>84</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AC33" s="2"/>
       <c r="AD33" t="s" s="2">
@@ -6209,7 +6215,7 @@
         <v>170</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>82</v>
@@ -6218,10 +6224,10 @@
         <v>94</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>84</v>
@@ -6233,30 +6239,30 @@
         <v>84</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="AQ33" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR33" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="D34" t="s" s="2">
         <v>84</v>
@@ -6281,16 +6287,16 @@
         <v>161</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>84</v>
@@ -6339,7 +6345,7 @@
         <v>84</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>82</v>
@@ -6348,13 +6354,13 @@
         <v>94</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>84</v>
@@ -6363,30 +6369,30 @@
         <v>84</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="AQ34" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR34" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="D35" t="s" s="2">
         <v>84</v>
@@ -6408,19 +6414,19 @@
         <v>95</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>84</v>
@@ -6469,7 +6475,7 @@
         <v>84</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>82</v>
@@ -6478,13 +6484,13 @@
         <v>94</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>84</v>
@@ -6493,30 +6499,30 @@
         <v>84</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="AQ35" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR35" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="D36" t="s" s="2">
         <v>84</v>
@@ -6541,16 +6547,16 @@
         <v>183</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>84</v>
@@ -6599,7 +6605,7 @@
         <v>84</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>82</v>
@@ -6608,13 +6614,13 @@
         <v>94</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>84</v>
@@ -6623,27 +6629,27 @@
         <v>84</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="AQ36" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR36" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6669,16 +6675,16 @@
         <v>183</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>84</v>
@@ -6706,10 +6712,10 @@
         <v>188</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>84</v>
@@ -6727,7 +6733,7 @@
         <v>84</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>82</v>
@@ -6736,13 +6742,13 @@
         <v>94</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>84</v>
@@ -6757,7 +6763,7 @@
         <v>137</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AQ37" t="s" s="2">
         <v>84</v>
@@ -6768,14 +6774,14 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -6797,16 +6803,16 @@
         <v>183</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>84</v>
@@ -6834,10 +6840,10 @@
         <v>188</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>84</v>
@@ -6855,7 +6861,7 @@
         <v>84</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>82</v>
@@ -6879,27 +6885,27 @@
         <v>84</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="AQ38" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR38" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6922,19 +6928,19 @@
         <v>84</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>84</v>
@@ -6983,7 +6989,7 @@
         <v>84</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
@@ -7010,10 +7016,10 @@
         <v>84</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="AQ39" t="s" s="2">
         <v>84</v>
@@ -7024,10 +7030,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7053,13 +7059,13 @@
         <v>183</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -7085,13 +7091,13 @@
         <v>84</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>84</v>
@@ -7109,7 +7115,7 @@
         <v>84</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>82</v>
@@ -7133,27 +7139,27 @@
         <v>84</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="AQ40" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR40" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7179,16 +7185,16 @@
         <v>183</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>84</v>
@@ -7213,13 +7219,13 @@
         <v>84</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>84</v>
@@ -7237,7 +7243,7 @@
         <v>84</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
@@ -7264,10 +7270,10 @@
         <v>84</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="AQ41" t="s" s="2">
         <v>84</v>
@@ -7278,10 +7284,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7304,16 +7310,16 @@
         <v>84</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7363,7 +7369,7 @@
         <v>84</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>82</v>
@@ -7387,27 +7393,27 @@
         <v>84</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="AQ42" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR42" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7430,16 +7436,16 @@
         <v>84</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -7489,7 +7495,7 @@
         <v>84</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>82</v>
@@ -7513,27 +7519,27 @@
         <v>84</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="AQ43" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR43" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7556,19 +7562,19 @@
         <v>84</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>84</v>
@@ -7617,7 +7623,7 @@
         <v>84</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>82</v>
@@ -7629,7 +7635,7 @@
         <v>84</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>84</v>
@@ -7644,10 +7650,10 @@
         <v>84</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="AQ44" t="s" s="2">
         <v>84</v>
@@ -7658,10 +7664,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7782,10 +7788,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7908,14 +7914,14 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7937,10 +7943,10 @@
         <v>140</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="N47" t="s" s="2">
         <v>143</v>
@@ -7995,7 +8001,7 @@
         <v>84</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
@@ -8036,10 +8042,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8062,13 +8068,13 @@
         <v>84</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -8119,7 +8125,7 @@
         <v>84</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -8128,7 +8134,7 @@
         <v>94</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>106</v>
@@ -8146,10 +8152,10 @@
         <v>84</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="AQ48" t="s" s="2">
         <v>84</v>
@@ -8160,10 +8166,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8186,13 +8192,13 @@
         <v>84</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -8243,7 +8249,7 @@
         <v>84</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
@@ -8252,7 +8258,7 @@
         <v>94</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="AJ49" t="s" s="2">
         <v>106</v>
@@ -8270,10 +8276,10 @@
         <v>84</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="AQ49" t="s" s="2">
         <v>84</v>
@@ -8284,10 +8290,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8313,16 +8319,16 @@
         <v>183</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>84</v>
@@ -8350,10 +8356,10 @@
         <v>118</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>84</v>
@@ -8371,7 +8377,7 @@
         <v>84</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
@@ -8395,13 +8401,13 @@
         <v>84</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="AQ50" t="s" s="2">
         <v>84</v>
@@ -8412,10 +8418,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8441,16 +8447,16 @@
         <v>183</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>84</v>
@@ -8475,13 +8481,13 @@
         <v>84</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>84</v>
@@ -8499,7 +8505,7 @@
         <v>84</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
@@ -8523,13 +8529,13 @@
         <v>84</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="AQ51" t="s" s="2">
         <v>84</v>
@@ -8540,10 +8546,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8566,17 +8572,17 @@
         <v>84</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>84</v>
@@ -8625,7 +8631,7 @@
         <v>84</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
@@ -8655,7 +8661,7 @@
         <v>84</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="AQ52" t="s" s="2">
         <v>84</v>
@@ -8666,10 +8672,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8695,10 +8701,10 @@
         <v>161</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8749,7 +8755,7 @@
         <v>84</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>82</v>
@@ -8776,10 +8782,10 @@
         <v>84</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="AQ53" t="s" s="2">
         <v>84</v>
@@ -8790,10 +8796,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8816,16 +8822,16 @@
         <v>95</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8875,7 +8881,7 @@
         <v>84</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>82</v>
@@ -8902,10 +8908,10 @@
         <v>84</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="AQ54" t="s" s="2">
         <v>84</v>
@@ -8916,10 +8922,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8942,16 +8948,16 @@
         <v>95</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -9001,7 +9007,7 @@
         <v>84</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>82</v>
@@ -9028,10 +9034,10 @@
         <v>84</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="AQ55" t="s" s="2">
         <v>84</v>
@@ -9042,10 +9048,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9068,19 +9074,19 @@
         <v>95</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>84</v>
@@ -9129,7 +9135,7 @@
         <v>84</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>82</v>
@@ -9156,10 +9162,10 @@
         <v>84</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="AQ56" t="s" s="2">
         <v>84</v>
@@ -9170,10 +9176,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9294,10 +9300,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9420,14 +9426,14 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -9449,10 +9455,10 @@
         <v>140</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="N59" t="s" s="2">
         <v>143</v>
@@ -9507,7 +9513,7 @@
         <v>84</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
@@ -9548,10 +9554,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9577,13 +9583,13 @@
         <v>183</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="O60" t="s" s="2">
         <v>277</v>
@@ -9611,13 +9617,13 @@
         <v>84</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>84</v>
@@ -9635,7 +9641,7 @@
         <v>84</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>94</v>
@@ -9659,7 +9665,7 @@
         <v>84</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>281</v>
@@ -9676,10 +9682,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9702,19 +9708,19 @@
         <v>95</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>84</v>
@@ -9763,7 +9769,7 @@
         <v>84</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>82</v>
@@ -9787,27 +9793,27 @@
         <v>84</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="AQ61" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR61" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9833,16 +9839,16 @@
         <v>183</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>84</v>
@@ -9870,10 +9876,10 @@
         <v>188</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>84</v>
@@ -9891,7 +9897,7 @@
         <v>84</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>82</v>
@@ -9900,7 +9906,7 @@
         <v>94</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>106</v>
@@ -9921,7 +9927,7 @@
         <v>137</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AQ62" t="s" s="2">
         <v>84</v>
@@ -9932,14 +9938,14 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -9961,16 +9967,16 @@
         <v>183</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>84</v>
@@ -9998,10 +10004,10 @@
         <v>188</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>84</v>
@@ -10019,7 +10025,7 @@
         <v>84</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>82</v>
@@ -10043,27 +10049,27 @@
         <v>84</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="AQ63" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR63" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10089,16 +10095,16 @@
         <v>85</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>84</v>
@@ -10147,7 +10153,7 @@
         <v>84</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>82</v>
@@ -10174,10 +10180,10 @@
         <v>84</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="AQ64" t="s" s="2">
         <v>84</v>

--- a/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.47.0</t>
+    <t>0.48.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-04T09:18:00+00:00</t>
+    <t>2024-05-06T08:00:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.48.0</t>
+    <t>0.49.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T08:00:03+00:00</t>
+    <t>2024-05-06T11:38:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.49.0</t>
+    <t>0.50.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T11:38:53+00:00</t>
+    <t>2024-05-08T06:31:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.50.0</t>
+    <t>0.51.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-08T06:31:45+00:00</t>
+    <t>2024-05-11T08:27:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2624" uniqueCount="540">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2624" uniqueCount="542">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.51.0</t>
+    <t>0.52.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-11T08:27:40+00:00</t>
+    <t>2024-05-19T08:28:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -632,10 +632,16 @@
     <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
+    <t>http://va.gov/fhir/identifiers/Sta3n&lt;stationNr&gt;/&lt;fileNr&gt;</t>
+  </si>
+  <si>
     <t>http://www.acme.com/identifiers/patient</t>
   </si>
   <si>
     <t>Identifier.system</t>
+  </si>
+  <si>
+    <t>1619-1: fixed value = http://va.gov/fhir/identifiers/Sta3n&lt;stationNr&gt;/&lt;fileNr&gt;</t>
   </si>
   <si>
     <t>CX.4 / EI-2-4</t>
@@ -3993,7 +3999,7 @@
         <v>94</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>84</v>
@@ -4024,10 +4030,10 @@
         <v>84</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>84</v>
+        <v>198</v>
       </c>
       <c r="T16" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="U16" t="s" s="2">
         <v>84</v>
@@ -4063,7 +4069,7 @@
         <v>84</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>82</v>
@@ -4078,7 +4084,7 @@
         <v>106</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>84</v>
+        <v>201</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>84</v>
@@ -4090,10 +4096,10 @@
         <v>84</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="AQ16" t="s" s="2">
         <v>84</v>
@@ -4104,10 +4110,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4133,13 +4139,13 @@
         <v>161</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -4153,7 +4159,7 @@
         <v>84</v>
       </c>
       <c r="T17" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="U17" t="s" s="2">
         <v>84</v>
@@ -4189,7 +4195,7 @@
         <v>84</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>82</v>
@@ -4204,7 +4210,7 @@
         <v>106</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>84</v>
@@ -4216,10 +4222,10 @@
         <v>84</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AP17" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="AQ17" t="s" s="2">
         <v>84</v>
@@ -4230,10 +4236,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4256,13 +4262,13 @@
         <v>95</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -4313,7 +4319,7 @@
         <v>84</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>82</v>
@@ -4340,10 +4346,10 @@
         <v>84</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AP18" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AQ18" t="s" s="2">
         <v>84</v>
@@ -4354,10 +4360,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4380,16 +4386,16 @@
         <v>95</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -4439,7 +4445,7 @@
         <v>84</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>82</v>
@@ -4466,10 +4472,10 @@
         <v>84</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AP19" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="AQ19" t="s" s="2">
         <v>84</v>
@@ -4480,14 +4486,14 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -4506,17 +4512,17 @@
         <v>95</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>84</v>
@@ -4565,7 +4571,7 @@
         <v>84</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>82</v>
@@ -4586,16 +4592,16 @@
         <v>84</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="AP20" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="AQ20" t="s" s="2">
         <v>84</v>
@@ -4606,14 +4612,14 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -4632,16 +4638,16 @@
         <v>95</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4691,7 +4697,7 @@
         <v>84</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>82</v>
@@ -4706,22 +4712,22 @@
         <v>106</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="AP21" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="AQ21" t="s" s="2">
         <v>84</v>
@@ -4732,10 +4738,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4761,16 +4767,16 @@
         <v>114</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>84</v>
@@ -4799,7 +4805,7 @@
       </c>
       <c r="Y22" s="2"/>
       <c r="Z22" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>84</v>
@@ -4817,7 +4823,7 @@
         <v>84</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>94</v>
@@ -4832,25 +4838,25 @@
         <v>106</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="AP22" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="AQ22" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AR22" t="s" s="2">
         <v>84</v>
@@ -4858,10 +4864,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4887,16 +4893,16 @@
         <v>183</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>84</v>
@@ -4906,7 +4912,7 @@
         <v>84</v>
       </c>
       <c r="S23" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="T23" t="s" s="2">
         <v>84</v>
@@ -4924,16 +4930,16 @@
         <v>118</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="AC23" s="2"/>
       <c r="AD23" t="s" s="2">
@@ -4943,7 +4949,7 @@
         <v>170</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>82</v>
@@ -4958,7 +4964,7 @@
         <v>106</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>84</v>
@@ -4973,10 +4979,10 @@
         <v>84</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AQ23" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AR23" t="s" s="2">
         <v>84</v>
@@ -4984,13 +4990,13 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>84</v>
@@ -5015,16 +5021,16 @@
         <v>183</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>84</v>
@@ -5034,7 +5040,7 @@
         <v>84</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="T24" t="s" s="2">
         <v>84</v>
@@ -5052,10 +5058,10 @@
         <v>118</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>84</v>
@@ -5073,7 +5079,7 @@
         <v>84</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>82</v>
@@ -5103,10 +5109,10 @@
         <v>84</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AQ24" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AR24" t="s" s="2">
         <v>84</v>
@@ -5114,14 +5120,14 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -5143,16 +5149,16 @@
         <v>183</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>84</v>
@@ -5181,7 +5187,7 @@
       </c>
       <c r="Y25" s="2"/>
       <c r="Z25" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>84</v>
@@ -5199,7 +5205,7 @@
         <v>84</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>94</v>
@@ -5220,30 +5226,30 @@
         <v>84</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="AQ25" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="AR25" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5266,19 +5272,19 @@
         <v>95</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>84</v>
@@ -5327,7 +5333,7 @@
         <v>84</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>82</v>
@@ -5342,25 +5348,25 @@
         <v>106</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="AQ26" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="AR26" t="s" s="2">
         <v>84</v>
@@ -5368,10 +5374,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5394,16 +5400,16 @@
         <v>95</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -5453,7 +5459,7 @@
         <v>84</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>82</v>
@@ -5480,13 +5486,13 @@
         <v>84</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="AQ27" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="AR27" t="s" s="2">
         <v>84</v>
@@ -5494,14 +5500,14 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -5520,19 +5526,19 @@
         <v>95</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>84</v>
@@ -5581,7 +5587,7 @@
         <v>84</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>82</v>
@@ -5602,19 +5608,19 @@
         <v>84</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AQ28" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="AR28" t="s" s="2">
         <v>84</v>
@@ -5622,14 +5628,14 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -5648,19 +5654,19 @@
         <v>95</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>84</v>
@@ -5697,7 +5703,7 @@
         <v>84</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="AC29" s="2"/>
       <c r="AD29" t="s" s="2">
@@ -5707,7 +5713,7 @@
         <v>170</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>82</v>
@@ -5716,10 +5722,10 @@
         <v>94</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>84</v>
@@ -5728,19 +5734,19 @@
         <v>84</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="AQ29" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="AR29" t="s" s="2">
         <v>84</v>
@@ -5748,16 +5754,16 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="D30" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -5776,19 +5782,19 @@
         <v>95</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>84</v>
@@ -5837,7 +5843,7 @@
         <v>84</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>82</v>
@@ -5846,31 +5852,31 @@
         <v>94</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="AQ30" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="AR30" t="s" s="2">
         <v>84</v>
@@ -5878,10 +5884,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5904,16 +5910,16 @@
         <v>95</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5963,7 +5969,7 @@
         <v>84</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>82</v>
@@ -5978,10 +5984,10 @@
         <v>106</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>84</v>
@@ -5990,13 +5996,13 @@
         <v>84</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="AQ31" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="AR31" t="s" s="2">
         <v>84</v>
@@ -6004,10 +6010,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6030,17 +6036,17 @@
         <v>95</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>84</v>
@@ -6089,7 +6095,7 @@
         <v>84</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>82</v>
@@ -6104,25 +6110,25 @@
         <v>106</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="AQ32" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="AR32" t="s" s="2">
         <v>84</v>
@@ -6130,10 +6136,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6156,19 +6162,19 @@
         <v>95</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>84</v>
@@ -6205,7 +6211,7 @@
         <v>84</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="AC33" s="2"/>
       <c r="AD33" t="s" s="2">
@@ -6215,7 +6221,7 @@
         <v>170</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>82</v>
@@ -6224,10 +6230,10 @@
         <v>94</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>84</v>
@@ -6239,30 +6245,30 @@
         <v>84</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="AQ33" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR33" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="D34" t="s" s="2">
         <v>84</v>
@@ -6287,16 +6293,16 @@
         <v>161</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>84</v>
@@ -6345,7 +6351,7 @@
         <v>84</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>82</v>
@@ -6354,13 +6360,13 @@
         <v>94</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>84</v>
@@ -6369,30 +6375,30 @@
         <v>84</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="AQ34" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR34" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="D35" t="s" s="2">
         <v>84</v>
@@ -6414,19 +6420,19 @@
         <v>95</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>84</v>
@@ -6475,7 +6481,7 @@
         <v>84</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>82</v>
@@ -6484,13 +6490,13 @@
         <v>94</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>84</v>
@@ -6499,30 +6505,30 @@
         <v>84</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="AQ35" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR35" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="D36" t="s" s="2">
         <v>84</v>
@@ -6547,16 +6553,16 @@
         <v>183</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>84</v>
@@ -6605,7 +6611,7 @@
         <v>84</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>82</v>
@@ -6614,13 +6620,13 @@
         <v>94</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>84</v>
@@ -6629,27 +6635,27 @@
         <v>84</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="AQ36" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR36" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6675,16 +6681,16 @@
         <v>183</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>84</v>
@@ -6712,10 +6718,10 @@
         <v>188</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>84</v>
@@ -6733,7 +6739,7 @@
         <v>84</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>82</v>
@@ -6742,13 +6748,13 @@
         <v>94</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>84</v>
@@ -6763,7 +6769,7 @@
         <v>137</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="AQ37" t="s" s="2">
         <v>84</v>
@@ -6774,14 +6780,14 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -6803,16 +6809,16 @@
         <v>183</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>84</v>
@@ -6840,10 +6846,10 @@
         <v>188</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>84</v>
@@ -6861,7 +6867,7 @@
         <v>84</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>82</v>
@@ -6885,27 +6891,27 @@
         <v>84</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="AQ38" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR38" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6928,19 +6934,19 @@
         <v>84</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>84</v>
@@ -6989,7 +6995,7 @@
         <v>84</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
@@ -7016,10 +7022,10 @@
         <v>84</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="AQ39" t="s" s="2">
         <v>84</v>
@@ -7030,10 +7036,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7059,13 +7065,13 @@
         <v>183</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -7091,13 +7097,13 @@
         <v>84</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>84</v>
@@ -7115,7 +7121,7 @@
         <v>84</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>82</v>
@@ -7139,27 +7145,27 @@
         <v>84</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AQ40" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR40" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7185,16 +7191,16 @@
         <v>183</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>84</v>
@@ -7219,13 +7225,13 @@
         <v>84</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>84</v>
@@ -7243,7 +7249,7 @@
         <v>84</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
@@ -7270,10 +7276,10 @@
         <v>84</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="AQ41" t="s" s="2">
         <v>84</v>
@@ -7284,10 +7290,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7310,16 +7316,16 @@
         <v>84</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7369,7 +7375,7 @@
         <v>84</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>82</v>
@@ -7393,27 +7399,27 @@
         <v>84</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="AQ42" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR42" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7436,16 +7442,16 @@
         <v>84</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -7495,7 +7501,7 @@
         <v>84</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>82</v>
@@ -7519,27 +7525,27 @@
         <v>84</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="AQ43" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR43" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7562,19 +7568,19 @@
         <v>84</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>84</v>
@@ -7623,7 +7629,7 @@
         <v>84</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>82</v>
@@ -7635,7 +7641,7 @@
         <v>84</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>84</v>
@@ -7650,10 +7656,10 @@
         <v>84</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="AQ44" t="s" s="2">
         <v>84</v>
@@ -7664,10 +7670,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7788,10 +7794,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7914,14 +7920,14 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7943,10 +7949,10 @@
         <v>140</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="N47" t="s" s="2">
         <v>143</v>
@@ -8001,7 +8007,7 @@
         <v>84</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
@@ -8042,10 +8048,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8068,13 +8074,13 @@
         <v>84</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -8125,7 +8131,7 @@
         <v>84</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -8134,7 +8140,7 @@
         <v>94</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>106</v>
@@ -8152,10 +8158,10 @@
         <v>84</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="AQ48" t="s" s="2">
         <v>84</v>
@@ -8166,10 +8172,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8192,13 +8198,13 @@
         <v>84</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -8249,7 +8255,7 @@
         <v>84</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
@@ -8258,7 +8264,7 @@
         <v>94</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="AJ49" t="s" s="2">
         <v>106</v>
@@ -8276,10 +8282,10 @@
         <v>84</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="AQ49" t="s" s="2">
         <v>84</v>
@@ -8290,10 +8296,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8319,16 +8325,16 @@
         <v>183</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>84</v>
@@ -8356,10 +8362,10 @@
         <v>118</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>84</v>
@@ -8377,7 +8383,7 @@
         <v>84</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
@@ -8401,13 +8407,13 @@
         <v>84</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="AQ50" t="s" s="2">
         <v>84</v>
@@ -8418,10 +8424,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8447,16 +8453,16 @@
         <v>183</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>84</v>
@@ -8481,13 +8487,13 @@
         <v>84</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>84</v>
@@ -8505,7 +8511,7 @@
         <v>84</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
@@ -8529,13 +8535,13 @@
         <v>84</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="AQ51" t="s" s="2">
         <v>84</v>
@@ -8546,10 +8552,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8572,17 +8578,17 @@
         <v>84</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>84</v>
@@ -8631,7 +8637,7 @@
         <v>84</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
@@ -8661,7 +8667,7 @@
         <v>84</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="AQ52" t="s" s="2">
         <v>84</v>
@@ -8672,10 +8678,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8701,10 +8707,10 @@
         <v>161</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8755,7 +8761,7 @@
         <v>84</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>82</v>
@@ -8782,10 +8788,10 @@
         <v>84</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="AQ53" t="s" s="2">
         <v>84</v>
@@ -8796,10 +8802,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8822,16 +8828,16 @@
         <v>95</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8881,7 +8887,7 @@
         <v>84</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>82</v>
@@ -8908,10 +8914,10 @@
         <v>84</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="AQ54" t="s" s="2">
         <v>84</v>
@@ -8922,10 +8928,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8948,16 +8954,16 @@
         <v>95</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -9007,7 +9013,7 @@
         <v>84</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>82</v>
@@ -9034,10 +9040,10 @@
         <v>84</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="AQ55" t="s" s="2">
         <v>84</v>
@@ -9048,10 +9054,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9074,19 +9080,19 @@
         <v>95</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>84</v>
@@ -9135,7 +9141,7 @@
         <v>84</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>82</v>
@@ -9162,10 +9168,10 @@
         <v>84</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="AQ56" t="s" s="2">
         <v>84</v>
@@ -9176,10 +9182,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9300,10 +9306,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9426,14 +9432,14 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -9455,10 +9461,10 @@
         <v>140</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="N59" t="s" s="2">
         <v>143</v>
@@ -9513,7 +9519,7 @@
         <v>84</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
@@ -9554,10 +9560,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9583,16 +9589,16 @@
         <v>183</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>84</v>
@@ -9617,13 +9623,13 @@
         <v>84</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>84</v>
@@ -9641,7 +9647,7 @@
         <v>84</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>94</v>
@@ -9665,16 +9671,16 @@
         <v>84</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="AQ60" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="AR60" t="s" s="2">
         <v>84</v>
@@ -9682,10 +9688,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9708,19 +9714,19 @@
         <v>95</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>84</v>
@@ -9769,7 +9775,7 @@
         <v>84</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>82</v>
@@ -9793,27 +9799,27 @@
         <v>84</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="AQ61" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR61" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9839,16 +9845,16 @@
         <v>183</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>84</v>
@@ -9876,10 +9882,10 @@
         <v>188</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>84</v>
@@ -9897,7 +9903,7 @@
         <v>84</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>82</v>
@@ -9906,7 +9912,7 @@
         <v>94</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>106</v>
@@ -9927,7 +9933,7 @@
         <v>137</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="AQ62" t="s" s="2">
         <v>84</v>
@@ -9938,14 +9944,14 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -9967,16 +9973,16 @@
         <v>183</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>84</v>
@@ -10004,10 +10010,10 @@
         <v>188</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>84</v>
@@ -10025,7 +10031,7 @@
         <v>84</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>82</v>
@@ -10049,27 +10055,27 @@
         <v>84</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="AQ63" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR63" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10095,16 +10101,16 @@
         <v>85</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>84</v>
@@ -10153,7 +10159,7 @@
         <v>84</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>82</v>
@@ -10180,10 +10186,10 @@
         <v>84</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="AQ64" t="s" s="2">
         <v>84</v>

--- a/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.52.0</t>
+    <t>0.53.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-19T08:28:17+00:00</t>
+    <t>2024-05-22T14:44:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.53.0</t>
+    <t>0.54.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-22T14:44:53+00:00</t>
+    <t>2024-05-25T10:26:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -632,7 +632,7 @@
     <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/identifiers/Sta3n&lt;stationNr&gt;/&lt;fileNr&gt;</t>
+    <t>http://va.gov/fhir/identifiers/Sta3n$stationNr/74</t>
   </si>
   <si>
     <t>http://www.acme.com/identifiers/patient</t>
@@ -641,7 +641,7 @@
     <t>Identifier.system</t>
   </si>
   <si>
-    <t>1619-1: fixed value = http://va.gov/fhir/identifiers/Sta3n&lt;stationNr&gt;/&lt;fileNr&gt;</t>
+    <t>1619-1: fixed value = http://va.gov/fhir/identifiers/Sta3n$stationNr/74</t>
   </si>
   <si>
     <t>CX.4 / EI-2-4</t>

--- a/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.54.0</t>
+    <t>0.57.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-25T10:26:15+00:00</t>
+    <t>2024-06-04T15:52:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -632,7 +632,7 @@
     <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/identifiers/Sta3n$stationNr/74</t>
+    <t>http://va.gov/identifiers/$Sta3n/74</t>
   </si>
   <si>
     <t>http://www.acme.com/identifiers/patient</t>
@@ -641,7 +641,7 @@
     <t>Identifier.system</t>
   </si>
   <si>
-    <t>1619-1: fixed value = http://va.gov/fhir/identifiers/Sta3n$stationNr/74</t>
+    <t>1619-1: fixed value = http://va.gov/identifiers/$Sta3n/74</t>
   </si>
   <si>
     <t>CX.4 / EI-2-4</t>

--- a/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-04T15:52:07+00:00</t>
+    <t>2024-06-11T05:38:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T05:38:55+00:00</t>
+    <t>2024-06-12T18:51:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.57.0</t>
+    <t>0.58.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-12T18:51:20+00:00</t>
+    <t>2024-06-14T11:56:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -773,7 +773,7 @@
     <t>To link an Observation to an Encounter use `encounter`.  See the  [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below for guidance on referencing another Observation.</t>
   </si>
   <si>
-    <t>1620: reference from REGISTERED EXAMS - EXAMINATIONS (70.02-50)</t>
+    <t>1620: reference from EXAMINATIONS - IEN (70.03-.001) case 70.03-17=this</t>
   </si>
   <si>
     <t>Event.partOf</t>

--- a/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.58.0</t>
+    <t>0.59.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-14T11:56:40+00:00</t>
+    <t>2024-06-21T15:05:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.61.0</t>
+    <t>0.62.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-24T18:59:55+00:00</t>
+    <t>2024-07-28T09:11:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.62.0</t>
+    <t>0.63.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-28T09:11:13+00:00</t>
+    <t>2024-07-31T09:58:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.63.0</t>
+    <t>0.64.311</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T09:58:27+00:00</t>
+    <t>2024-07-31T19:09:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.311</t>
+    <t>0.64.312</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T19:09:08+00:00</t>
+    <t>2024-08-02T13:01:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.312</t>
+    <t>0.64.316</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-02T13:01:18+00:00</t>
+    <t>2024-08-04T09:05:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -760,7 +760,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationAdministration|MedicationDispense|MedicationStatement|Procedure|Immunization|ImagingStudy)
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/ProcedureSurgery)
 </t>
   </si>
   <si>
@@ -2045,7 +2045,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="111.11328125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="110.76953125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.316</t>
+    <t>0.64.318</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-04T09:05:29+00:00</t>
+    <t>2024-08-05T15:01:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.318</t>
+    <t>0.65.329</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-05T15:01:43+00:00</t>
+    <t>2024-08-13T08:01:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.329</t>
+    <t>0.65.332</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T08:01:15+00:00</t>
+    <t>2024-08-13T15:06:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.332</t>
+    <t>0.65.334</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T15:06:38+00:00</t>
+    <t>2024-08-14T15:16:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-14T15:16:17+00:00</t>
+    <t>2024-08-17T06:29:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.334</t>
+    <t>0.65.339</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-17T06:29:49+00:00</t>
+    <t>2024-08-18T10:15:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.339</t>
+    <t>0.65.341</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-18T10:15:47+00:00</t>
+    <t>2024-08-20T15:42:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.341</t>
+    <t>0.65.343</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-20T15:42:57+00:00</t>
+    <t>2024-08-24T10:06:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.343</t>
+    <t>0.65.345</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-24T10:06:05+00:00</t>
+    <t>2024-08-26T15:27:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.345</t>
+    <t>0.65.348</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-26T15:27:18+00:00</t>
+    <t>2024-09-15T08:33:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.348</t>
+    <t>0.66.354</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-15T08:33:43+00:00</t>
+    <t>2024-09-19T08:45:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.354</t>
+    <t>0.66.364</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-19T08:45:12+00:00</t>
+    <t>2024-10-02T18:53:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.364</t>
+    <t>0.66.366</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-02T18:53:29+00:00</t>
+    <t>2024-10-11T07:57:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -915,7 +915,7 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-patient)
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Patient)
 </t>
   </si>
   <si>

--- a/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.366</t>
+    <t>0.66.367</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-11T07:57:28+00:00</t>
+    <t>2024-10-13T09:59:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.367</t>
+    <t>0.67.369</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-13T09:59:39+00:00</t>
+    <t>2024-10-18T16:05:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.369</t>
+    <t>0.67.370</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-18T16:05:33+00:00</t>
+    <t>2024-10-20T09:02:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -760,7 +760,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/ProcedureSurgery)
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/ProcedureSurgeryProcedure)
 </t>
   </si>
   <si>

--- a/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.370</t>
+    <t>0.67.378</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-20T09:02:32+00:00</t>
+    <t>2024-10-30T12:26:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.378</t>
+    <t>0.67.381</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-30T12:26:51+00:00</t>
+    <t>2024-11-03T11:50:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.381</t>
+    <t>0.68.397</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-03T11:50:46+00:00</t>
+    <t>2024-11-10T10:13:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -915,7 +915,7 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Patient)
+    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-patient)
 </t>
   </si>
   <si>

--- a/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.397</t>
+    <t>0.68.401</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-10T10:13:24+00:00</t>
+    <t>2024-11-13T21:40:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.401</t>
+    <t>0.68.419</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-13T21:40:45+00:00</t>
+    <t>2024-11-25T07:50:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -800,7 +800,7 @@
     <t>Need to track the status of individual results. Some results are finalized before the whole report is finalized.</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFImageStatusRadNuc</t>
+    <t>http://va.gov/fhir/ValueSet/ImageStatusRadNuc</t>
   </si>
   <si>
     <t>1623: terminologyMaps using VF_ImageStatusRadNuc on RAD/NUC MED REPORTS - REPORT STATUS (74-5)</t>

--- a/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.419</t>
+    <t>0.68.424</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-25T07:50:24+00:00</t>
+    <t>2024-11-30T14:03:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.424</t>
+    <t>0.68.425</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T14:03:16+00:00</t>
+    <t>2024-11-30T15:07:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.425</t>
+    <t>0.69.436</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T15:07:22+00:00</t>
+    <t>2024-12-04T11:34:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.436</t>
+    <t>0.69.437</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T11:34:53+00:00</t>
+    <t>2024-12-04T16:25:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.437</t>
+    <t>0.69.438</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T16:25:11+00:00</t>
+    <t>2024-12-06T17:18:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.439</t>
+    <t>0.69.440</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-07T11:18:15+00:00</t>
+    <t>2024-12-08T09:28:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1131,7 +1131,7 @@
     <t>SStaff.RadiologyNuclearMedicineReport.VerifyingPhysicianStaffIEN</t>
   </si>
   <si>
-    <t>Documents.DocumentExtension.CareProviders</t>
+    <t>Documents.Extension[DocumentExtension].CareProviders</t>
   </si>
   <si>
     <t>Event.performer.actor</t>
@@ -2087,7 +2087,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="99.80078125" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="62.34375" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="51.63671875" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="54.453125" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="247.40625" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="255.0" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.440</t>
+    <t>0.69.442</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-08T09:28:43+00:00</t>
+    <t>2024-12-11T20:06:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.442</t>
+    <t>0.69.448</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T20:06:32+00:00</t>
+    <t>2024-12-21T10:24:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file RAD/NUC MED REPORTS (74) to us-core-observation-imaging</t>
+    <t>This StructureDefinition contains the maps for VistA file RAD/NUC MED REPORTS (74) to us-core-observation-imaging.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2688" uniqueCount="547">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2688" uniqueCount="548">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.448</t>
+    <t>1.1.467</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-21T10:24:25+00:00</t>
+    <t>2025-01-04T09:38:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -898,6 +898,9 @@
   </si>
   <si>
     <t>http://hl7.org/fhir/us/core/ValueSet/us-core-diagnosticreport-report-and-note-codes</t>
+  </si>
+  <si>
+    <t>2196: target not supported</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -5308,7 +5311,7 @@
         <v>107</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>85</v>
+        <v>283</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>85</v>
@@ -5317,30 +5320,30 @@
         <v>85</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AQ25" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AR25" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AS25" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5363,19 +5366,19 @@
         <v>96</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>85</v>
@@ -5424,7 +5427,7 @@
         <v>85</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>83</v>
@@ -5439,28 +5442,28 @@
         <v>107</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AQ26" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AR26" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AS26" t="s" s="2">
         <v>85</v>
@@ -5468,10 +5471,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5494,16 +5497,16 @@
         <v>96</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -5553,7 +5556,7 @@
         <v>85</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>83</v>
@@ -5583,13 +5586,13 @@
         <v>85</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AQ27" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AR27" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AS27" t="s" s="2">
         <v>85</v>
@@ -5597,14 +5600,14 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -5623,19 +5626,19 @@
         <v>96</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>85</v>
@@ -5684,7 +5687,7 @@
         <v>85</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>83</v>
@@ -5708,19 +5711,19 @@
         <v>85</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AQ28" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AR28" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AS28" t="s" s="2">
         <v>85</v>
@@ -5728,14 +5731,14 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -5754,19 +5757,19 @@
         <v>96</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>85</v>
@@ -5803,7 +5806,7 @@
         <v>85</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AC29" s="2"/>
       <c r="AD29" t="s" s="2">
@@ -5813,7 +5816,7 @@
         <v>171</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>83</v>
@@ -5822,10 +5825,10 @@
         <v>95</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>85</v>
@@ -5837,19 +5840,19 @@
         <v>85</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AQ29" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AR29" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AS29" t="s" s="2">
         <v>85</v>
@@ -5857,16 +5860,16 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D30" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -5885,19 +5888,19 @@
         <v>96</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>85</v>
@@ -5946,7 +5949,7 @@
         <v>85</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>83</v>
@@ -5955,34 +5958,34 @@
         <v>95</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AQ30" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AR30" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AS30" t="s" s="2">
         <v>85</v>
@@ -5990,10 +5993,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6016,16 +6019,16 @@
         <v>96</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -6075,7 +6078,7 @@
         <v>85</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>83</v>
@@ -6090,13 +6093,13 @@
         <v>107</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>85</v>
@@ -6105,13 +6108,13 @@
         <v>85</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AQ31" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AR31" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AS31" t="s" s="2">
         <v>85</v>
@@ -6119,10 +6122,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6145,17 +6148,17 @@
         <v>96</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>85</v>
@@ -6204,7 +6207,7 @@
         <v>85</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>83</v>
@@ -6219,28 +6222,28 @@
         <v>107</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AQ32" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AR32" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AS32" t="s" s="2">
         <v>85</v>
@@ -6248,10 +6251,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6274,19 +6277,19 @@
         <v>96</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>85</v>
@@ -6323,7 +6326,7 @@
         <v>85</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AC33" s="2"/>
       <c r="AD33" t="s" s="2">
@@ -6333,7 +6336,7 @@
         <v>171</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>83</v>
@@ -6342,10 +6345,10 @@
         <v>95</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>85</v>
@@ -6360,30 +6363,30 @@
         <v>85</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AQ33" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AR33" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS33" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D34" t="s" s="2">
         <v>85</v>
@@ -6408,16 +6411,16 @@
         <v>162</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>85</v>
@@ -6466,7 +6469,7 @@
         <v>85</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>83</v>
@@ -6475,13 +6478,13 @@
         <v>95</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>85</v>
@@ -6493,30 +6496,30 @@
         <v>85</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AQ34" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AR34" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS34" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D35" t="s" s="2">
         <v>85</v>
@@ -6538,19 +6541,19 @@
         <v>96</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>85</v>
@@ -6599,7 +6602,7 @@
         <v>85</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>83</v>
@@ -6608,13 +6611,13 @@
         <v>95</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>85</v>
@@ -6626,30 +6629,30 @@
         <v>85</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AQ35" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AR35" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS35" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D36" t="s" s="2">
         <v>85</v>
@@ -6674,16 +6677,16 @@
         <v>184</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>85</v>
@@ -6732,7 +6735,7 @@
         <v>85</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>83</v>
@@ -6741,13 +6744,13 @@
         <v>95</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>85</v>
@@ -6759,27 +6762,27 @@
         <v>85</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AQ36" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AR36" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS36" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6805,16 +6808,16 @@
         <v>184</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>85</v>
@@ -6842,10 +6845,10 @@
         <v>189</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>85</v>
@@ -6863,7 +6866,7 @@
         <v>85</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>83</v>
@@ -6872,13 +6875,13 @@
         <v>95</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>85</v>
@@ -6896,7 +6899,7 @@
         <v>138</v>
       </c>
       <c r="AQ37" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AR37" t="s" s="2">
         <v>85</v>
@@ -6907,14 +6910,14 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -6936,16 +6939,16 @@
         <v>184</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>85</v>
@@ -6973,10 +6976,10 @@
         <v>189</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>85</v>
@@ -6994,7 +6997,7 @@
         <v>85</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>83</v>
@@ -7021,27 +7024,27 @@
         <v>85</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AQ38" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AR38" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS38" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7064,19 +7067,19 @@
         <v>85</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>85</v>
@@ -7125,7 +7128,7 @@
         <v>85</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>83</v>
@@ -7155,10 +7158,10 @@
         <v>85</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AQ39" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AR39" t="s" s="2">
         <v>85</v>
@@ -7169,10 +7172,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7198,13 +7201,13 @@
         <v>184</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -7230,13 +7233,13 @@
         <v>85</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>85</v>
@@ -7254,7 +7257,7 @@
         <v>85</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>83</v>
@@ -7281,27 +7284,27 @@
         <v>85</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AQ40" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AR40" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS40" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7327,16 +7330,16 @@
         <v>184</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>85</v>
@@ -7361,13 +7364,13 @@
         <v>85</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>85</v>
@@ -7385,7 +7388,7 @@
         <v>85</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>83</v>
@@ -7415,10 +7418,10 @@
         <v>85</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AQ41" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AR41" t="s" s="2">
         <v>85</v>
@@ -7429,10 +7432,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7455,16 +7458,16 @@
         <v>85</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7514,7 +7517,7 @@
         <v>85</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>83</v>
@@ -7541,27 +7544,27 @@
         <v>85</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AQ42" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AR42" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS42" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7584,16 +7587,16 @@
         <v>85</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -7643,7 +7646,7 @@
         <v>85</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>83</v>
@@ -7670,27 +7673,27 @@
         <v>85</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AQ43" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AR43" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS43" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7713,19 +7716,19 @@
         <v>85</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>85</v>
@@ -7774,7 +7777,7 @@
         <v>85</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>83</v>
@@ -7786,7 +7789,7 @@
         <v>85</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>85</v>
@@ -7804,10 +7807,10 @@
         <v>85</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AQ44" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AR44" t="s" s="2">
         <v>85</v>
@@ -7818,10 +7821,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7945,10 +7948,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8074,14 +8077,14 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -8103,10 +8106,10 @@
         <v>141</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="N47" t="s" s="2">
         <v>144</v>
@@ -8161,7 +8164,7 @@
         <v>85</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>83</v>
@@ -8205,10 +8208,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8231,13 +8234,13 @@
         <v>85</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -8288,7 +8291,7 @@
         <v>85</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>83</v>
@@ -8297,7 +8300,7 @@
         <v>95</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>107</v>
@@ -8318,10 +8321,10 @@
         <v>85</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AQ48" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AR48" t="s" s="2">
         <v>85</v>
@@ -8332,10 +8335,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8358,13 +8361,13 @@
         <v>85</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -8415,7 +8418,7 @@
         <v>85</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>83</v>
@@ -8424,7 +8427,7 @@
         <v>95</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AJ49" t="s" s="2">
         <v>107</v>
@@ -8445,10 +8448,10 @@
         <v>85</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AQ49" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AR49" t="s" s="2">
         <v>85</v>
@@ -8459,10 +8462,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8488,16 +8491,16 @@
         <v>184</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>85</v>
@@ -8525,10 +8528,10 @@
         <v>119</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>85</v>
@@ -8546,7 +8549,7 @@
         <v>85</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>83</v>
@@ -8573,13 +8576,13 @@
         <v>85</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AQ50" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AR50" t="s" s="2">
         <v>85</v>
@@ -8590,10 +8593,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8619,16 +8622,16 @@
         <v>184</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>85</v>
@@ -8653,13 +8656,13 @@
         <v>85</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>85</v>
@@ -8677,7 +8680,7 @@
         <v>85</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>83</v>
@@ -8704,13 +8707,13 @@
         <v>85</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AQ51" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AR51" t="s" s="2">
         <v>85</v>
@@ -8721,10 +8724,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8747,17 +8750,17 @@
         <v>85</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>85</v>
@@ -8806,7 +8809,7 @@
         <v>85</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>83</v>
@@ -8839,7 +8842,7 @@
         <v>85</v>
       </c>
       <c r="AQ52" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AR52" t="s" s="2">
         <v>85</v>
@@ -8850,10 +8853,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8879,10 +8882,10 @@
         <v>162</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8933,7 +8936,7 @@
         <v>85</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>83</v>
@@ -8963,10 +8966,10 @@
         <v>85</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AQ53" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AR53" t="s" s="2">
         <v>85</v>
@@ -8977,10 +8980,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9003,16 +9006,16 @@
         <v>96</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -9062,7 +9065,7 @@
         <v>85</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>83</v>
@@ -9092,10 +9095,10 @@
         <v>85</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AQ54" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AR54" t="s" s="2">
         <v>85</v>
@@ -9106,10 +9109,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9132,16 +9135,16 @@
         <v>96</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -9191,7 +9194,7 @@
         <v>85</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>83</v>
@@ -9221,10 +9224,10 @@
         <v>85</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AQ55" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AR55" t="s" s="2">
         <v>85</v>
@@ -9235,10 +9238,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9261,19 +9264,19 @@
         <v>96</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>85</v>
@@ -9322,7 +9325,7 @@
         <v>85</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>83</v>
@@ -9352,10 +9355,10 @@
         <v>85</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AQ56" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AR56" t="s" s="2">
         <v>85</v>
@@ -9366,10 +9369,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9493,10 +9496,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9622,14 +9625,14 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -9651,10 +9654,10 @@
         <v>141</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="N59" t="s" s="2">
         <v>144</v>
@@ -9709,7 +9712,7 @@
         <v>85</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>83</v>
@@ -9753,10 +9756,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9782,13 +9785,13 @@
         <v>184</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="O60" t="s" s="2">
         <v>281</v>
@@ -9816,13 +9819,13 @@
         <v>85</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>85</v>
@@ -9840,7 +9843,7 @@
         <v>85</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>95</v>
@@ -9867,16 +9870,16 @@
         <v>85</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AQ60" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AR60" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AS60" t="s" s="2">
         <v>85</v>
@@ -9884,10 +9887,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9910,19 +9913,19 @@
         <v>96</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>85</v>
@@ -9971,7 +9974,7 @@
         <v>85</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>83</v>
@@ -9998,27 +10001,27 @@
         <v>85</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AQ61" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AR61" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS61" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10044,16 +10047,16 @@
         <v>184</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>85</v>
@@ -10081,10 +10084,10 @@
         <v>189</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>85</v>
@@ -10102,7 +10105,7 @@
         <v>85</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>83</v>
@@ -10111,7 +10114,7 @@
         <v>95</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>107</v>
@@ -10135,7 +10138,7 @@
         <v>138</v>
       </c>
       <c r="AQ62" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AR62" t="s" s="2">
         <v>85</v>
@@ -10146,14 +10149,14 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -10175,16 +10178,16 @@
         <v>184</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>85</v>
@@ -10212,10 +10215,10 @@
         <v>189</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>85</v>
@@ -10233,7 +10236,7 @@
         <v>85</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>83</v>
@@ -10260,27 +10263,27 @@
         <v>85</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AQ63" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AR63" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS63" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10306,16 +10309,16 @@
         <v>86</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>85</v>
@@ -10364,7 +10367,7 @@
         <v>85</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>83</v>
@@ -10394,10 +10397,10 @@
         <v>85</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AQ64" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AR64" t="s" s="2">
         <v>85</v>

--- a/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.467</t>
+    <t>1.1.468</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T09:38:39+00:00</t>
+    <t>2025-01-04T15:04:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.468</t>
+    <t>1.1.477</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T15:04:27+00:00</t>
+    <t>2025-01-07T16:27:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.477</t>
+    <t>1.1.478</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-07T16:27:08+00:00</t>
+    <t>2025-01-13T09:39:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.478</t>
+    <t>1.1.487</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-13T09:39:57+00:00</t>
+    <t>2025-01-17T12:09:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -671,7 +671,7 @@
     <t>Identifier.value</t>
   </si>
   <si>
-    <t>1619: source value from RAD/NUC MED REPORTS - IEN (74-.001)</t>
+    <t>1619: source value based on RAD/NUC MED REPORTS - IEN (74-.001)</t>
   </si>
   <si>
     <t>CX.1 / EI.1</t>
@@ -776,7 +776,7 @@
     <t>To link an Observation to an Encounter use `encounter`.  See the  [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below for guidance on referencing another Observation.</t>
   </si>
   <si>
-    <t>1620: reference from REGISTERED EXAMS - EXAMINATIONS (70.02-50)</t>
+    <t>1620: reference based on REGISTERED EXAMS - EXAMINATIONS (70.02-50)</t>
   </si>
   <si>
     <t>Event.partOf</t>
@@ -940,7 +940,7 @@
     <t>Observations have no value if you don't know who or what they're about.</t>
   </si>
   <si>
-    <t>1633: reference from RAD/NUC MED REPORTS - PATIENT NAME (74-2)</t>
+    <t>1633: reference based on RAD/NUC MED REPORTS - PATIENT NAME (74-2)</t>
   </si>
   <si>
     <t>SStaff.RadiologyNuclearMedicineReport.PatientIEN</t>
@@ -1072,7 +1072,7 @@
 </t>
   </si>
   <si>
-    <t>1636: source value from RAD/NUC MED REPORTS - EXAM DATE/TIME (74-3)</t>
+    <t>1636: source value based on RAD/NUC MED REPORTS - EXAM DATE/TIME (74-3)</t>
   </si>
   <si>
     <t>SStaff.RadiologyNuclearMedicineReport.ExamDateTime</t>
@@ -1094,7 +1094,7 @@
     <t>For Observations that don’t require review and verification, it may be the same as the [`lastUpdated` ](http://hl7.org/fhir/R4/resource-definitions.html#Meta.lastUpdated) time of the resource itself.  For Observations that do require review and verification for certain updates, it might not be the same as the `lastUpdated` time of the resource itself due to a non-clinically significant update that doesn’t require the new version to be reviewed and verified again.</t>
   </si>
   <si>
-    <t>1639: source value from RAD/NUC MED REPORTS - VERIFIED DATE (74-7)</t>
+    <t>1639: source value based on RAD/NUC MED REPORTS - VERIFIED DATE (74-7)</t>
   </si>
   <si>
     <t>SStaff.RadiologyNuclearMedicineReport.VerifiedDateTime</t>
@@ -1128,7 +1128,7 @@
     <t>May give a degree of confidence in the observation and also indicates where follow-up questions should be directed.</t>
   </si>
   <si>
-    <t>1642: source value from RAD/NUC MED REPORTS - VERIFYING PHYSICIAN (74-9)</t>
+    <t>1642: source value based on RAD/NUC MED REPORTS - VERIFYING PHYSICIAN (74-9)</t>
   </si>
   <si>
     <t>SStaff.RadiologyNuclearMedicineReport.VerifyingPhysicianStaffIEN</t>
@@ -1194,7 +1194,7 @@
     <t>valueString</t>
   </si>
   <si>
-    <t>1647: source value from RAD/NUC MED REPORTS - IMPRESSION TEXT (74-300)</t>
+    <t>1647: source value based on RAD/NUC MED REPORTS - IMPRESSION TEXT (74-300)</t>
   </si>
   <si>
     <t>Observation.value[x]:valueQuantity</t>

--- a/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.487</t>
+    <t>1.1.491</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T12:09:20+00:00</t>
+    <t>2025-01-17T13:37:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.491</t>
+    <t>1.1.494</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T13:37:46+00:00</t>
+    <t>2025-01-25T09:28:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.494</t>
+    <t>1.1.500</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-25T09:28:03+00:00</t>
+    <t>2025-02-01T09:13:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2688" uniqueCount="548">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2689" uniqueCount="549">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.500</t>
+    <t>1.2.512</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-01T09:13:38+00:00</t>
+    <t>2025-02-05T16:47:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -801,6 +801,9 @@
   </si>
   <si>
     <t>Need to track the status of individual results. Some results are finalized before the whole report is finalized.</t>
+  </si>
+  <si>
+    <t>see mapping [VF_ImageStatusRadNuc](ConceptMap-VF-ImageStatusRadNuc.html)</t>
   </si>
   <si>
     <t>http://va.gov/fhir/ValueSet/ImageStatusRadNuc</t>
@@ -4885,9 +4888,11 @@
       <c r="X22" t="s" s="2">
         <v>178</v>
       </c>
-      <c r="Y22" s="2"/>
+      <c r="Y22" t="s" s="2">
+        <v>253</v>
+      </c>
       <c r="Z22" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>85</v>
@@ -4920,28 +4925,28 @@
         <v>107</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AP22" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AQ22" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AR22" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AS22" t="s" s="2">
         <v>85</v>
@@ -4949,10 +4954,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4978,16 +4983,16 @@
         <v>184</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>85</v>
@@ -4997,7 +5002,7 @@
         <v>85</v>
       </c>
       <c r="S23" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="T23" t="s" s="2">
         <v>85</v>
@@ -5015,16 +5020,16 @@
         <v>119</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AC23" s="2"/>
       <c r="AD23" t="s" s="2">
@@ -5034,7 +5039,7 @@
         <v>171</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>83</v>
@@ -5049,7 +5054,7 @@
         <v>107</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>85</v>
@@ -5067,10 +5072,10 @@
         <v>85</v>
       </c>
       <c r="AQ23" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AR23" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AS23" t="s" s="2">
         <v>85</v>
@@ -5078,13 +5083,13 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>85</v>
@@ -5109,16 +5114,16 @@
         <v>184</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>85</v>
@@ -5128,7 +5133,7 @@
         <v>85</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="T24" t="s" s="2">
         <v>85</v>
@@ -5146,10 +5151,10 @@
         <v>119</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>85</v>
@@ -5167,7 +5172,7 @@
         <v>85</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>83</v>
@@ -5200,10 +5205,10 @@
         <v>85</v>
       </c>
       <c r="AQ24" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AR24" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AS24" t="s" s="2">
         <v>85</v>
@@ -5211,14 +5216,14 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -5240,16 +5245,16 @@
         <v>184</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>85</v>
@@ -5278,7 +5283,7 @@
       </c>
       <c r="Y25" s="2"/>
       <c r="Z25" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>85</v>
@@ -5296,7 +5301,7 @@
         <v>85</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>95</v>
@@ -5311,7 +5316,7 @@
         <v>107</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>85</v>
@@ -5320,30 +5325,30 @@
         <v>85</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AQ25" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AR25" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AS25" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5366,19 +5371,19 @@
         <v>96</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>85</v>
@@ -5427,7 +5432,7 @@
         <v>85</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>83</v>
@@ -5442,28 +5447,28 @@
         <v>107</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AQ26" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AR26" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AS26" t="s" s="2">
         <v>85</v>
@@ -5471,10 +5476,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5497,16 +5502,16 @@
         <v>96</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -5556,7 +5561,7 @@
         <v>85</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>83</v>
@@ -5586,13 +5591,13 @@
         <v>85</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AQ27" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AR27" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AS27" t="s" s="2">
         <v>85</v>
@@ -5600,14 +5605,14 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -5626,19 +5631,19 @@
         <v>96</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>85</v>
@@ -5687,7 +5692,7 @@
         <v>85</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>83</v>
@@ -5711,19 +5716,19 @@
         <v>85</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AQ28" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AR28" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AS28" t="s" s="2">
         <v>85</v>
@@ -5731,14 +5736,14 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -5757,19 +5762,19 @@
         <v>96</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>85</v>
@@ -5806,7 +5811,7 @@
         <v>85</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AC29" s="2"/>
       <c r="AD29" t="s" s="2">
@@ -5816,7 +5821,7 @@
         <v>171</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>83</v>
@@ -5825,10 +5830,10 @@
         <v>95</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>85</v>
@@ -5840,19 +5845,19 @@
         <v>85</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AQ29" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AR29" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AS29" t="s" s="2">
         <v>85</v>
@@ -5860,16 +5865,16 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="D30" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -5888,19 +5893,19 @@
         <v>96</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>85</v>
@@ -5949,7 +5954,7 @@
         <v>85</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>83</v>
@@ -5958,34 +5963,34 @@
         <v>95</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AQ30" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AR30" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AS30" t="s" s="2">
         <v>85</v>
@@ -5993,10 +5998,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6019,16 +6024,16 @@
         <v>96</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -6078,7 +6083,7 @@
         <v>85</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>83</v>
@@ -6093,13 +6098,13 @@
         <v>107</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>85</v>
@@ -6108,13 +6113,13 @@
         <v>85</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AQ31" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AR31" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AS31" t="s" s="2">
         <v>85</v>
@@ -6122,10 +6127,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6148,17 +6153,17 @@
         <v>96</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>85</v>
@@ -6207,7 +6212,7 @@
         <v>85</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>83</v>
@@ -6222,28 +6227,28 @@
         <v>107</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AQ32" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AR32" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AS32" t="s" s="2">
         <v>85</v>
@@ -6251,10 +6256,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6277,19 +6282,19 @@
         <v>96</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>85</v>
@@ -6326,7 +6331,7 @@
         <v>85</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AC33" s="2"/>
       <c r="AD33" t="s" s="2">
@@ -6336,7 +6341,7 @@
         <v>171</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>83</v>
@@ -6345,10 +6350,10 @@
         <v>95</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>85</v>
@@ -6363,30 +6368,30 @@
         <v>85</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AQ33" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AR33" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS33" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D34" t="s" s="2">
         <v>85</v>
@@ -6411,16 +6416,16 @@
         <v>162</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>85</v>
@@ -6469,7 +6474,7 @@
         <v>85</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>83</v>
@@ -6478,13 +6483,13 @@
         <v>95</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>85</v>
@@ -6496,30 +6501,30 @@
         <v>85</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AQ34" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AR34" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS34" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="D35" t="s" s="2">
         <v>85</v>
@@ -6541,19 +6546,19 @@
         <v>96</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>85</v>
@@ -6602,7 +6607,7 @@
         <v>85</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>83</v>
@@ -6611,13 +6616,13 @@
         <v>95</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>85</v>
@@ -6629,30 +6634,30 @@
         <v>85</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AQ35" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AR35" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS35" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="D36" t="s" s="2">
         <v>85</v>
@@ -6677,16 +6682,16 @@
         <v>184</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>85</v>
@@ -6735,7 +6740,7 @@
         <v>85</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>83</v>
@@ -6744,13 +6749,13 @@
         <v>95</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>85</v>
@@ -6762,27 +6767,27 @@
         <v>85</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AQ36" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AR36" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS36" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6808,16 +6813,16 @@
         <v>184</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>85</v>
@@ -6845,10 +6850,10 @@
         <v>189</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>85</v>
@@ -6866,7 +6871,7 @@
         <v>85</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>83</v>
@@ -6875,13 +6880,13 @@
         <v>95</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>85</v>
@@ -6899,7 +6904,7 @@
         <v>138</v>
       </c>
       <c r="AQ37" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AR37" t="s" s="2">
         <v>85</v>
@@ -6910,14 +6915,14 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -6939,16 +6944,16 @@
         <v>184</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>85</v>
@@ -6976,10 +6981,10 @@
         <v>189</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>85</v>
@@ -6997,7 +7002,7 @@
         <v>85</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>83</v>
@@ -7024,27 +7029,27 @@
         <v>85</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AQ38" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AR38" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS38" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7067,19 +7072,19 @@
         <v>85</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>85</v>
@@ -7128,7 +7133,7 @@
         <v>85</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>83</v>
@@ -7158,10 +7163,10 @@
         <v>85</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AQ39" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AR39" t="s" s="2">
         <v>85</v>
@@ -7172,10 +7177,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7201,13 +7206,13 @@
         <v>184</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -7233,13 +7238,13 @@
         <v>85</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>85</v>
@@ -7257,7 +7262,7 @@
         <v>85</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>83</v>
@@ -7284,27 +7289,27 @@
         <v>85</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AQ40" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AR40" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS40" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7330,16 +7335,16 @@
         <v>184</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>85</v>
@@ -7364,13 +7369,13 @@
         <v>85</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>85</v>
@@ -7388,7 +7393,7 @@
         <v>85</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>83</v>
@@ -7418,10 +7423,10 @@
         <v>85</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AQ41" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AR41" t="s" s="2">
         <v>85</v>
@@ -7432,10 +7437,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7458,16 +7463,16 @@
         <v>85</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7517,7 +7522,7 @@
         <v>85</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>83</v>
@@ -7544,27 +7549,27 @@
         <v>85</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AQ42" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AR42" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS42" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7587,16 +7592,16 @@
         <v>85</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -7646,7 +7651,7 @@
         <v>85</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>83</v>
@@ -7673,27 +7678,27 @@
         <v>85</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AQ43" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AR43" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS43" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7716,19 +7721,19 @@
         <v>85</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>85</v>
@@ -7777,7 +7782,7 @@
         <v>85</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>83</v>
@@ -7789,7 +7794,7 @@
         <v>85</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>85</v>
@@ -7807,10 +7812,10 @@
         <v>85</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AQ44" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AR44" t="s" s="2">
         <v>85</v>
@@ -7821,10 +7826,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7948,10 +7953,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8077,14 +8082,14 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -8106,10 +8111,10 @@
         <v>141</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="N47" t="s" s="2">
         <v>144</v>
@@ -8164,7 +8169,7 @@
         <v>85</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>83</v>
@@ -8208,10 +8213,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8234,13 +8239,13 @@
         <v>85</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -8291,7 +8296,7 @@
         <v>85</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>83</v>
@@ -8300,7 +8305,7 @@
         <v>95</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>107</v>
@@ -8321,10 +8326,10 @@
         <v>85</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AQ48" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AR48" t="s" s="2">
         <v>85</v>
@@ -8335,10 +8340,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8361,13 +8366,13 @@
         <v>85</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -8418,7 +8423,7 @@
         <v>85</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>83</v>
@@ -8427,7 +8432,7 @@
         <v>95</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AJ49" t="s" s="2">
         <v>107</v>
@@ -8448,10 +8453,10 @@
         <v>85</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AQ49" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AR49" t="s" s="2">
         <v>85</v>
@@ -8462,10 +8467,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8491,16 +8496,16 @@
         <v>184</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>85</v>
@@ -8528,10 +8533,10 @@
         <v>119</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>85</v>
@@ -8549,7 +8554,7 @@
         <v>85</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>83</v>
@@ -8576,13 +8581,13 @@
         <v>85</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AQ50" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AR50" t="s" s="2">
         <v>85</v>
@@ -8593,10 +8598,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8622,16 +8627,16 @@
         <v>184</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>85</v>
@@ -8656,13 +8661,13 @@
         <v>85</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>85</v>
@@ -8680,7 +8685,7 @@
         <v>85</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>83</v>
@@ -8707,13 +8712,13 @@
         <v>85</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AQ51" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AR51" t="s" s="2">
         <v>85</v>
@@ -8724,10 +8729,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8750,17 +8755,17 @@
         <v>85</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>85</v>
@@ -8809,7 +8814,7 @@
         <v>85</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>83</v>
@@ -8842,7 +8847,7 @@
         <v>85</v>
       </c>
       <c r="AQ52" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AR52" t="s" s="2">
         <v>85</v>
@@ -8853,10 +8858,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8882,10 +8887,10 @@
         <v>162</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8936,7 +8941,7 @@
         <v>85</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>83</v>
@@ -8966,10 +8971,10 @@
         <v>85</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AQ53" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AR53" t="s" s="2">
         <v>85</v>
@@ -8980,10 +8985,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9006,16 +9011,16 @@
         <v>96</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -9065,7 +9070,7 @@
         <v>85</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>83</v>
@@ -9095,10 +9100,10 @@
         <v>85</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AQ54" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AR54" t="s" s="2">
         <v>85</v>
@@ -9109,10 +9114,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9135,16 +9140,16 @@
         <v>96</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -9194,7 +9199,7 @@
         <v>85</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>83</v>
@@ -9224,10 +9229,10 @@
         <v>85</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AQ55" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AR55" t="s" s="2">
         <v>85</v>
@@ -9238,10 +9243,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9264,19 +9269,19 @@
         <v>96</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>85</v>
@@ -9325,7 +9330,7 @@
         <v>85</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>83</v>
@@ -9355,10 +9360,10 @@
         <v>85</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AQ56" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AR56" t="s" s="2">
         <v>85</v>
@@ -9369,10 +9374,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9496,10 +9501,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9625,14 +9630,14 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -9654,10 +9659,10 @@
         <v>141</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="N59" t="s" s="2">
         <v>144</v>
@@ -9712,7 +9717,7 @@
         <v>85</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>83</v>
@@ -9756,10 +9761,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9785,16 +9790,16 @@
         <v>184</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>85</v>
@@ -9819,13 +9824,13 @@
         <v>85</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>85</v>
@@ -9843,7 +9848,7 @@
         <v>85</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>95</v>
@@ -9870,16 +9875,16 @@
         <v>85</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AQ60" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AR60" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AS60" t="s" s="2">
         <v>85</v>
@@ -9887,10 +9892,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9913,19 +9918,19 @@
         <v>96</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>85</v>
@@ -9974,7 +9979,7 @@
         <v>85</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>83</v>
@@ -10001,27 +10006,27 @@
         <v>85</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AQ61" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AR61" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS61" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10047,16 +10052,16 @@
         <v>184</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>85</v>
@@ -10084,10 +10089,10 @@
         <v>189</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>85</v>
@@ -10105,7 +10110,7 @@
         <v>85</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>83</v>
@@ -10114,7 +10119,7 @@
         <v>95</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>107</v>
@@ -10138,7 +10143,7 @@
         <v>138</v>
       </c>
       <c r="AQ62" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AR62" t="s" s="2">
         <v>85</v>
@@ -10149,14 +10154,14 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -10178,16 +10183,16 @@
         <v>184</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>85</v>
@@ -10215,10 +10220,10 @@
         <v>189</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>85</v>
@@ -10236,7 +10241,7 @@
         <v>85</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>83</v>
@@ -10263,27 +10268,27 @@
         <v>85</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AQ63" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AR63" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS63" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10309,16 +10314,16 @@
         <v>86</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>85</v>
@@ -10367,7 +10372,7 @@
         <v>85</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>83</v>
@@ -10397,10 +10402,10 @@
         <v>85</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AQ64" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AR64" t="s" s="2">
         <v>85</v>

--- a/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T16:47:13+00:00</t>
+    <t>2025-02-05T17:20:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.512</t>
+    <t>1.2.520</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T17:20:26+00:00</t>
+    <t>2025-02-08T12:00:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.520</t>
+    <t>1.2.529</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-08T12:00:09+00:00</t>
+    <t>2025-02-20T14:56:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AS$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AS$62</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2689" uniqueCount="549">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2603" uniqueCount="542">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.529</t>
+    <t>1.2.531</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:56:35+00:00</t>
+    <t>2025-02-22T09:54:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -846,6 +846,28 @@
   </si>
   <si>
     <t>Used for filtering what observations are retrieved and displayed.</t>
+  </si>
+  <si>
+    <t>Codes for high level observation categories.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pattern:$this}
+</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
+  </si>
+  <si>
+    <t>FiveWs.class</t>
+  </si>
+  <si>
+    <t>Observation.category:imaging</t>
+  </si>
+  <si>
+    <t>imaging</t>
   </si>
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
@@ -856,29 +878,7 @@
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
-    <t>Codes for high level observation categories.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pattern:$this}
-</t>
-  </si>
-  <si>
     <t>1624: fixed value = http://terminology.hl7.org/CodeSystem/observation-category#imaging</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
-  </si>
-  <si>
-    <t>FiveWs.class</t>
-  </si>
-  <si>
-    <t>Observation.category:imaging</t>
-  </si>
-  <si>
-    <t>imaging</t>
   </si>
   <si>
     <t>Observation.code</t>
@@ -927,7 +927,7 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-patient)
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Patient)
 </t>
   </si>
   <si>
@@ -1198,28 +1198,6 @@
   </si>
   <si>
     <t>1647: source value based on RAD/NUC MED REPORTS - IMPRESSION TEXT (74-300)</t>
-  </si>
-  <si>
-    <t>Observation.value[x]:valueQuantity</t>
-  </si>
-  <si>
-    <t>valueQuantity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quantity
-</t>
-  </si>
-  <si>
-    <t>1797: target not supported</t>
-  </si>
-  <si>
-    <t>Observation.value[x]:valueCodeableConcept</t>
-  </si>
-  <si>
-    <t>valueCodeableConcept</t>
-  </si>
-  <si>
-    <t>1798: target not supported</t>
   </si>
   <si>
     <t>Observation.dataAbsentReason</t>
@@ -2053,12 +2031,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AS64"/>
+  <dimension ref="A1:AS62"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="44.67578125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="44.67578125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="22.25390625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="17.96484375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -5002,7 +4980,7 @@
         <v>85</v>
       </c>
       <c r="S23" t="s" s="2">
-        <v>268</v>
+        <v>85</v>
       </c>
       <c r="T23" t="s" s="2">
         <v>85</v>
@@ -5020,16 +4998,16 @@
         <v>119</v>
       </c>
       <c r="Y23" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="Z23" t="s" s="2">
         <v>269</v>
       </c>
-      <c r="Z23" t="s" s="2">
+      <c r="AA23" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB23" t="s" s="2">
         <v>270</v>
-      </c>
-      <c r="AA23" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AB23" t="s" s="2">
-        <v>271</v>
       </c>
       <c r="AC23" s="2"/>
       <c r="AD23" t="s" s="2">
@@ -5054,28 +5032,28 @@
         <v>107</v>
       </c>
       <c r="AK23" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AL23" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AM23" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AN23" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AO23" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AP23" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AQ23" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="AR23" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="AL23" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AM23" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AN23" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AO23" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AP23" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AQ23" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="AR23" t="s" s="2">
-        <v>274</v>
       </c>
       <c r="AS23" t="s" s="2">
         <v>85</v>
@@ -5083,13 +5061,13 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B24" t="s" s="2">
         <v>263</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>85</v>
@@ -5133,7 +5111,7 @@
         <v>85</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="T24" t="s" s="2">
         <v>85</v>
@@ -5151,10 +5129,10 @@
         <v>119</v>
       </c>
       <c r="Y24" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="Z24" t="s" s="2">
         <v>269</v>
-      </c>
-      <c r="Z24" t="s" s="2">
-        <v>270</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>85</v>
@@ -5187,7 +5165,7 @@
         <v>107</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>85</v>
+        <v>276</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>85</v>
@@ -5205,10 +5183,10 @@
         <v>85</v>
       </c>
       <c r="AQ24" t="s" s="2">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="AR24" t="s" s="2">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="AS24" t="s" s="2">
         <v>85</v>
@@ -6521,11 +6499,9 @@
         <v>378</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="C35" t="s" s="2">
-        <v>379</v>
-      </c>
+        <v>378</v>
+      </c>
+      <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
         <v>85</v>
       </c>
@@ -6543,22 +6519,22 @@
         <v>85</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="L35" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="M35" t="s" s="2">
         <v>380</v>
       </c>
-      <c r="L35" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>366</v>
-      </c>
       <c r="N35" t="s" s="2">
-        <v>367</v>
+        <v>381</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>368</v>
+        <v>382</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>85</v>
@@ -6583,13 +6559,13 @@
         <v>85</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>85</v>
+        <v>189</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>85</v>
+        <v>383</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>85</v>
+        <v>384</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>85</v>
@@ -6607,7 +6583,7 @@
         <v>85</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>363</v>
+        <v>378</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>83</v>
@@ -6616,13 +6592,13 @@
         <v>95</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>369</v>
+        <v>385</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>370</v>
+        <v>107</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>85</v>
@@ -6634,64 +6610,62 @@
         <v>85</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>371</v>
+        <v>85</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>372</v>
+        <v>138</v>
       </c>
       <c r="AQ35" t="s" s="2">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="AR35" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS35" t="s" s="2">
-        <v>374</v>
+        <v>85</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="C36" t="s" s="2">
-        <v>383</v>
-      </c>
+        <v>388</v>
+      </c>
+      <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>85</v>
+        <v>389</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>85</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K36" t="s" s="2">
         <v>184</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>365</v>
+        <v>390</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>366</v>
+        <v>391</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>367</v>
+        <v>392</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>368</v>
+        <v>393</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>85</v>
@@ -6716,13 +6690,13 @@
         <v>85</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>85</v>
+        <v>189</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>85</v>
+        <v>394</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>85</v>
+        <v>395</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>85</v>
@@ -6740,22 +6714,22 @@
         <v>85</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>363</v>
+        <v>388</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>369</v>
+        <v>85</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>370</v>
+        <v>107</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>384</v>
+        <v>85</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>85</v>
@@ -6767,27 +6741,27 @@
         <v>85</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>371</v>
+        <v>396</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>372</v>
+        <v>397</v>
       </c>
       <c r="AQ36" t="s" s="2">
-        <v>373</v>
+        <v>398</v>
       </c>
       <c r="AR36" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS36" t="s" s="2">
-        <v>374</v>
+        <v>399</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>385</v>
+        <v>400</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>385</v>
+        <v>400</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6798,10 +6772,10 @@
         <v>83</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>85</v>
@@ -6810,19 +6784,19 @@
         <v>85</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>184</v>
+        <v>401</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>386</v>
+        <v>402</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>387</v>
+        <v>403</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>388</v>
+        <v>404</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>389</v>
+        <v>405</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>85</v>
@@ -6847,13 +6821,13 @@
         <v>85</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>189</v>
+        <v>85</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>390</v>
+        <v>85</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>391</v>
+        <v>85</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>85</v>
@@ -6871,22 +6845,22 @@
         <v>85</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>385</v>
+        <v>400</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>392</v>
+        <v>85</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>393</v>
+        <v>85</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>85</v>
@@ -6901,10 +6875,10 @@
         <v>85</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>138</v>
+        <v>406</v>
       </c>
       <c r="AQ37" t="s" s="2">
-        <v>394</v>
+        <v>407</v>
       </c>
       <c r="AR37" t="s" s="2">
         <v>85</v>
@@ -6915,21 +6889,21 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>395</v>
+        <v>408</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>395</v>
+        <v>408</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>396</v>
+        <v>85</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>85</v>
@@ -6944,17 +6918,15 @@
         <v>184</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>397</v>
+        <v>409</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>398</v>
+        <v>410</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>400</v>
-      </c>
+        <v>411</v>
+      </c>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>85</v>
       </c>
@@ -6978,13 +6950,13 @@
         <v>85</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>189</v>
+        <v>412</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>401</v>
+        <v>413</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>402</v>
+        <v>414</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>85</v>
@@ -7002,13 +6974,13 @@
         <v>85</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>395</v>
+        <v>408</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>85</v>
@@ -7029,27 +7001,27 @@
         <v>85</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>403</v>
+        <v>415</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>404</v>
+        <v>416</v>
       </c>
       <c r="AQ38" t="s" s="2">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="AR38" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS38" t="s" s="2">
-        <v>406</v>
+        <v>418</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>407</v>
+        <v>419</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>407</v>
+        <v>419</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7060,7 +7032,7 @@
         <v>83</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>85</v>
@@ -7072,19 +7044,19 @@
         <v>85</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>408</v>
+        <v>184</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>409</v>
+        <v>420</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>410</v>
+        <v>421</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>411</v>
+        <v>422</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>412</v>
+        <v>423</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>85</v>
@@ -7109,13 +7081,13 @@
         <v>85</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>85</v>
+        <v>412</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>85</v>
+        <v>424</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>85</v>
+        <v>425</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>85</v>
@@ -7133,13 +7105,13 @@
         <v>85</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>407</v>
+        <v>419</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>85</v>
@@ -7163,10 +7135,10 @@
         <v>85</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>413</v>
+        <v>426</v>
       </c>
       <c r="AQ39" t="s" s="2">
-        <v>414</v>
+        <v>427</v>
       </c>
       <c r="AR39" t="s" s="2">
         <v>85</v>
@@ -7177,10 +7149,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>415</v>
+        <v>428</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>415</v>
+        <v>428</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7203,16 +7175,16 @@
         <v>85</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>184</v>
+        <v>429</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>416</v>
+        <v>430</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>417</v>
+        <v>431</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>418</v>
+        <v>432</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -7238,13 +7210,13 @@
         <v>85</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>419</v>
+        <v>85</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>420</v>
+        <v>85</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>421</v>
+        <v>85</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>85</v>
@@ -7262,7 +7234,7 @@
         <v>85</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>415</v>
+        <v>428</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>83</v>
@@ -7289,27 +7261,27 @@
         <v>85</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>422</v>
+        <v>433</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>423</v>
+        <v>434</v>
       </c>
       <c r="AQ40" t="s" s="2">
-        <v>424</v>
+        <v>435</v>
       </c>
       <c r="AR40" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS40" t="s" s="2">
-        <v>425</v>
+        <v>436</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>426</v>
+        <v>437</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>426</v>
+        <v>437</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7332,20 +7304,18 @@
         <v>85</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>184</v>
+        <v>438</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>427</v>
+        <v>439</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>428</v>
+        <v>440</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>430</v>
-      </c>
+        <v>441</v>
+      </c>
+      <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>85</v>
       </c>
@@ -7369,13 +7339,13 @@
         <v>85</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>419</v>
+        <v>85</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>431</v>
+        <v>85</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>432</v>
+        <v>85</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>85</v>
@@ -7393,7 +7363,7 @@
         <v>85</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>426</v>
+        <v>437</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>83</v>
@@ -7420,27 +7390,27 @@
         <v>85</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>85</v>
+        <v>442</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>433</v>
+        <v>443</v>
       </c>
       <c r="AQ41" t="s" s="2">
-        <v>434</v>
+        <v>444</v>
       </c>
       <c r="AR41" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS41" t="s" s="2">
-        <v>85</v>
+        <v>445</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>435</v>
+        <v>446</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>435</v>
+        <v>446</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7451,7 +7421,7 @@
         <v>83</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>85</v>
@@ -7463,18 +7433,20 @@
         <v>85</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>436</v>
+        <v>447</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>437</v>
+        <v>448</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>438</v>
+        <v>449</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="O42" s="2"/>
+        <v>450</v>
+      </c>
+      <c r="O42" t="s" s="2">
+        <v>451</v>
+      </c>
       <c r="P42" t="s" s="2">
         <v>85</v>
       </c>
@@ -7522,19 +7494,19 @@
         <v>85</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>435</v>
+        <v>446</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>107</v>
+        <v>452</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>85</v>
@@ -7549,27 +7521,27 @@
         <v>85</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>440</v>
+        <v>85</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>441</v>
+        <v>453</v>
       </c>
       <c r="AQ42" t="s" s="2">
-        <v>442</v>
+        <v>454</v>
       </c>
       <c r="AR42" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS42" t="s" s="2">
-        <v>443</v>
+        <v>85</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>444</v>
+        <v>455</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>444</v>
+        <v>455</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7592,17 +7564,15 @@
         <v>85</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>445</v>
+        <v>162</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>446</v>
+        <v>163</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>448</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="N43" s="2"/>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>85</v>
@@ -7651,7 +7621,7 @@
         <v>85</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>444</v>
+        <v>165</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>83</v>
@@ -7663,7 +7633,7 @@
         <v>85</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>85</v>
@@ -7678,31 +7648,31 @@
         <v>85</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>449</v>
+        <v>85</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>450</v>
+        <v>85</v>
       </c>
       <c r="AQ43" t="s" s="2">
-        <v>451</v>
+        <v>166</v>
       </c>
       <c r="AR43" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS43" t="s" s="2">
-        <v>452</v>
+        <v>85</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>85</v>
+        <v>140</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -7721,20 +7691,18 @@
         <v>85</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>454</v>
+        <v>141</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>455</v>
+        <v>142</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>456</v>
+        <v>168</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>458</v>
-      </c>
+        <v>144</v>
+      </c>
+      <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>85</v>
       </c>
@@ -7782,7 +7750,7 @@
         <v>85</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>453</v>
+        <v>172</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>83</v>
@@ -7794,7 +7762,7 @@
         <v>85</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>459</v>
+        <v>146</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>85</v>
@@ -7812,10 +7780,10 @@
         <v>85</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>460</v>
+        <v>85</v>
       </c>
       <c r="AQ44" t="s" s="2">
-        <v>461</v>
+        <v>166</v>
       </c>
       <c r="AR44" t="s" s="2">
         <v>85</v>
@@ -7826,42 +7794,46 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>85</v>
+        <v>458</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>85</v>
       </c>
       <c r="I45" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>162</v>
+        <v>141</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>163</v>
+        <v>459</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="N45" s="2"/>
-      <c r="O45" s="2"/>
+        <v>460</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="O45" t="s" s="2">
+        <v>150</v>
+      </c>
       <c r="P45" t="s" s="2">
         <v>85</v>
       </c>
@@ -7909,19 +7881,19 @@
         <v>85</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>165</v>
+        <v>461</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>85</v>
+        <v>146</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>85</v>
@@ -7942,7 +7914,7 @@
         <v>85</v>
       </c>
       <c r="AQ45" t="s" s="2">
-        <v>166</v>
+        <v>138</v>
       </c>
       <c r="AR45" t="s" s="2">
         <v>85</v>
@@ -7953,21 +7925,21 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>140</v>
+        <v>85</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>85</v>
@@ -7979,17 +7951,15 @@
         <v>85</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>141</v>
+        <v>463</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>142</v>
+        <v>464</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>144</v>
-      </c>
+        <v>465</v>
+      </c>
+      <c r="N46" s="2"/>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>85</v>
@@ -8038,19 +8008,19 @@
         <v>85</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>172</v>
+        <v>462</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>85</v>
+        <v>466</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>85</v>
@@ -8068,10 +8038,10 @@
         <v>85</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>85</v>
+        <v>467</v>
       </c>
       <c r="AQ46" t="s" s="2">
-        <v>166</v>
+        <v>468</v>
       </c>
       <c r="AR46" t="s" s="2">
         <v>85</v>
@@ -8082,46 +8052,42 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>465</v>
+        <v>85</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>85</v>
       </c>
       <c r="I47" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>141</v>
+        <v>463</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>150</v>
-      </c>
+        <v>471</v>
+      </c>
+      <c r="N47" s="2"/>
+      <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>85</v>
       </c>
@@ -8169,19 +8135,19 @@
         <v>85</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>85</v>
+        <v>466</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>85</v>
@@ -8199,10 +8165,10 @@
         <v>85</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>85</v>
+        <v>467</v>
       </c>
       <c r="AQ47" t="s" s="2">
-        <v>138</v>
+        <v>472</v>
       </c>
       <c r="AR47" t="s" s="2">
         <v>85</v>
@@ -8213,10 +8179,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8239,16 +8205,20 @@
         <v>85</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>470</v>
+        <v>184</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="N48" s="2"/>
-      <c r="O48" s="2"/>
+        <v>475</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="O48" t="s" s="2">
+        <v>477</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>85</v>
       </c>
@@ -8272,13 +8242,13 @@
         <v>85</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>85</v>
+        <v>119</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>85</v>
+        <v>478</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>85</v>
+        <v>479</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>85</v>
@@ -8296,7 +8266,7 @@
         <v>85</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>83</v>
@@ -8305,7 +8275,7 @@
         <v>95</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>473</v>
+        <v>85</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>107</v>
@@ -8323,13 +8293,13 @@
         <v>85</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>85</v>
+        <v>480</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>474</v>
+        <v>481</v>
       </c>
       <c r="AQ48" t="s" s="2">
-        <v>475</v>
+        <v>398</v>
       </c>
       <c r="AR48" t="s" s="2">
         <v>85</v>
@@ -8340,10 +8310,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8354,7 +8324,7 @@
         <v>83</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>85</v>
@@ -8366,16 +8336,20 @@
         <v>85</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>470</v>
+        <v>184</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>477</v>
+        <v>483</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="N49" s="2"/>
-      <c r="O49" s="2"/>
+        <v>484</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="O49" t="s" s="2">
+        <v>486</v>
+      </c>
       <c r="P49" t="s" s="2">
         <v>85</v>
       </c>
@@ -8399,13 +8373,13 @@
         <v>85</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>85</v>
+        <v>412</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>85</v>
+        <v>487</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>85</v>
+        <v>488</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>85</v>
@@ -8423,16 +8397,16 @@
         <v>85</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>473</v>
+        <v>85</v>
       </c>
       <c r="AJ49" t="s" s="2">
         <v>107</v>
@@ -8450,13 +8424,13 @@
         <v>85</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>85</v>
+        <v>480</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>474</v>
+        <v>481</v>
       </c>
       <c r="AQ49" t="s" s="2">
-        <v>479</v>
+        <v>398</v>
       </c>
       <c r="AR49" t="s" s="2">
         <v>85</v>
@@ -8467,10 +8441,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>480</v>
+        <v>489</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>480</v>
+        <v>489</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8493,19 +8467,17 @@
         <v>85</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>184</v>
+        <v>490</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>481</v>
+        <v>491</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>483</v>
-      </c>
+        <v>492</v>
+      </c>
+      <c r="N50" s="2"/>
       <c r="O50" t="s" s="2">
-        <v>484</v>
+        <v>493</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>85</v>
@@ -8530,13 +8502,13 @@
         <v>85</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>119</v>
+        <v>85</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>485</v>
+        <v>85</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>486</v>
+        <v>85</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>85</v>
@@ -8554,7 +8526,7 @@
         <v>85</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>480</v>
+        <v>489</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>83</v>
@@ -8581,13 +8553,13 @@
         <v>85</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>487</v>
+        <v>85</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>488</v>
+        <v>85</v>
       </c>
       <c r="AQ50" t="s" s="2">
-        <v>405</v>
+        <v>494</v>
       </c>
       <c r="AR50" t="s" s="2">
         <v>85</v>
@@ -8598,10 +8570,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>489</v>
+        <v>495</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>489</v>
+        <v>495</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8612,7 +8584,7 @@
         <v>83</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>85</v>
@@ -8624,20 +8596,16 @@
         <v>85</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>184</v>
+        <v>162</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>490</v>
+        <v>496</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>493</v>
-      </c>
+        <v>497</v>
+      </c>
+      <c r="N51" s="2"/>
+      <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>85</v>
       </c>
@@ -8661,37 +8629,37 @@
         <v>85</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>419</v>
+        <v>85</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>494</v>
+        <v>85</v>
       </c>
       <c r="Z51" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA51" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB51" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC51" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD51" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE51" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF51" t="s" s="2">
         <v>495</v>
       </c>
-      <c r="AA51" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AB51" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AC51" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AD51" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AE51" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AF51" t="s" s="2">
-        <v>489</v>
-      </c>
       <c r="AG51" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>85</v>
@@ -8712,13 +8680,13 @@
         <v>85</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>487</v>
+        <v>85</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>488</v>
+        <v>467</v>
       </c>
       <c r="AQ51" t="s" s="2">
-        <v>405</v>
+        <v>498</v>
       </c>
       <c r="AR51" t="s" s="2">
         <v>85</v>
@@ -8729,10 +8697,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8743,7 +8711,7 @@
         <v>83</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>85</v>
@@ -8752,21 +8720,21 @@
         <v>85</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>499</v>
-      </c>
-      <c r="N52" s="2"/>
-      <c r="O52" t="s" s="2">
-        <v>500</v>
-      </c>
+        <v>502</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>85</v>
       </c>
@@ -8814,13 +8782,13 @@
         <v>85</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>85</v>
@@ -8844,10 +8812,10 @@
         <v>85</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>85</v>
+        <v>504</v>
       </c>
       <c r="AQ52" t="s" s="2">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="AR52" t="s" s="2">
         <v>85</v>
@@ -8858,10 +8826,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8872,7 +8840,7 @@
         <v>83</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>85</v>
@@ -8881,18 +8849,20 @@
         <v>85</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>162</v>
+        <v>507</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>504</v>
-      </c>
-      <c r="N53" s="2"/>
+        <v>509</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>510</v>
+      </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>85</v>
@@ -8941,13 +8911,13 @@
         <v>85</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>85</v>
@@ -8971,10 +8941,10 @@
         <v>85</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>474</v>
+        <v>504</v>
       </c>
       <c r="AQ53" t="s" s="2">
-        <v>505</v>
+        <v>511</v>
       </c>
       <c r="AR53" t="s" s="2">
         <v>85</v>
@@ -8985,10 +8955,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>506</v>
+        <v>512</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>506</v>
+        <v>512</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9011,18 +8981,20 @@
         <v>96</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>507</v>
+        <v>447</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>510</v>
-      </c>
-      <c r="O54" s="2"/>
+        <v>515</v>
+      </c>
+      <c r="O54" t="s" s="2">
+        <v>516</v>
+      </c>
       <c r="P54" t="s" s="2">
         <v>85</v>
       </c>
@@ -9070,7 +9042,7 @@
         <v>85</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>506</v>
+        <v>512</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>83</v>
@@ -9100,10 +9072,10 @@
         <v>85</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c r="AQ54" t="s" s="2">
-        <v>512</v>
+        <v>518</v>
       </c>
       <c r="AR54" t="s" s="2">
         <v>85</v>
@@ -9114,10 +9086,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>513</v>
+        <v>519</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>513</v>
+        <v>519</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9128,7 +9100,7 @@
         <v>83</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>85</v>
@@ -9137,20 +9109,18 @@
         <v>85</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>514</v>
+        <v>162</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>515</v>
+        <v>163</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>516</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>517</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="N55" s="2"/>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>85</v>
@@ -9199,19 +9169,19 @@
         <v>85</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>513</v>
+        <v>165</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>85</v>
@@ -9229,10 +9199,10 @@
         <v>85</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>511</v>
+        <v>85</v>
       </c>
       <c r="AQ55" t="s" s="2">
-        <v>518</v>
+        <v>166</v>
       </c>
       <c r="AR55" t="s" s="2">
         <v>85</v>
@@ -9243,14 +9213,14 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>85</v>
+        <v>140</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -9266,23 +9236,21 @@
         <v>85</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>454</v>
+        <v>141</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>520</v>
+        <v>142</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>521</v>
+        <v>168</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>522</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>523</v>
-      </c>
+        <v>144</v>
+      </c>
+      <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>85</v>
       </c>
@@ -9330,7 +9298,7 @@
         <v>85</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>519</v>
+        <v>172</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>83</v>
@@ -9342,7 +9310,7 @@
         <v>85</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>85</v>
@@ -9360,10 +9328,10 @@
         <v>85</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>524</v>
+        <v>85</v>
       </c>
       <c r="AQ56" t="s" s="2">
-        <v>525</v>
+        <v>166</v>
       </c>
       <c r="AR56" t="s" s="2">
         <v>85</v>
@@ -9374,42 +9342,46 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>526</v>
+        <v>521</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>526</v>
+        <v>521</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>85</v>
+        <v>458</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>85</v>
       </c>
       <c r="I57" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>162</v>
+        <v>141</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>163</v>
+        <v>459</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="N57" s="2"/>
-      <c r="O57" s="2"/>
+        <v>460</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="O57" t="s" s="2">
+        <v>150</v>
+      </c>
       <c r="P57" t="s" s="2">
         <v>85</v>
       </c>
@@ -9457,19 +9429,19 @@
         <v>85</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>165</v>
+        <v>461</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>85</v>
+        <v>146</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>85</v>
@@ -9490,7 +9462,7 @@
         <v>85</v>
       </c>
       <c r="AQ57" t="s" s="2">
-        <v>166</v>
+        <v>138</v>
       </c>
       <c r="AR57" t="s" s="2">
         <v>85</v>
@@ -9501,21 +9473,21 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>527</v>
+        <v>522</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>527</v>
+        <v>522</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>140</v>
+        <v>85</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>85</v>
@@ -9524,21 +9496,23 @@
         <v>85</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>141</v>
+        <v>184</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>142</v>
+        <v>523</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>168</v>
+        <v>524</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="O58" s="2"/>
+        <v>525</v>
+      </c>
+      <c r="O58" t="s" s="2">
+        <v>282</v>
+      </c>
       <c r="P58" t="s" s="2">
         <v>85</v>
       </c>
@@ -9562,13 +9536,13 @@
         <v>85</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>85</v>
+        <v>412</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>85</v>
+        <v>526</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>85</v>
+        <v>527</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>85</v>
@@ -9586,19 +9560,19 @@
         <v>85</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>172</v>
+        <v>522</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>85</v>
@@ -9613,16 +9587,16 @@
         <v>85</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>85</v>
+        <v>528</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>85</v>
+        <v>287</v>
       </c>
       <c r="AQ58" t="s" s="2">
-        <v>166</v>
+        <v>288</v>
       </c>
       <c r="AR58" t="s" s="2">
-        <v>85</v>
+        <v>289</v>
       </c>
       <c r="AS58" t="s" s="2">
         <v>85</v>
@@ -9630,45 +9604,45 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>465</v>
+        <v>85</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>85</v>
       </c>
       <c r="I59" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="J59" t="s" s="2">
         <v>96</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>141</v>
+        <v>364</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>466</v>
+        <v>530</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>467</v>
+        <v>366</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>144</v>
+        <v>531</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>150</v>
+        <v>368</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>85</v>
@@ -9717,19 +9691,19 @@
         <v>85</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>468</v>
+        <v>529</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>85</v>
@@ -9744,27 +9718,27 @@
         <v>85</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>85</v>
+        <v>532</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>85</v>
+        <v>372</v>
       </c>
       <c r="AQ59" t="s" s="2">
-        <v>138</v>
+        <v>373</v>
       </c>
       <c r="AR59" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS59" t="s" s="2">
-        <v>85</v>
+        <v>374</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9772,7 +9746,7 @@
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="G60" t="s" s="2">
         <v>95</v>
@@ -9784,22 +9758,22 @@
         <v>85</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K60" t="s" s="2">
         <v>184</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>282</v>
+        <v>382</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>85</v>
@@ -9824,40 +9798,40 @@
         <v>85</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>419</v>
+        <v>189</v>
       </c>
       <c r="Y60" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="Z60" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="AA60" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB60" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD60" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE60" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF60" t="s" s="2">
         <v>533</v>
       </c>
-      <c r="Z60" t="s" s="2">
-        <v>534</v>
-      </c>
-      <c r="AA60" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AB60" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AC60" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AD60" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AE60" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AF60" t="s" s="2">
-        <v>529</v>
-      </c>
       <c r="AG60" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="AH60" t="s" s="2">
         <v>95</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>85</v>
+        <v>537</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>107</v>
@@ -9875,16 +9849,16 @@
         <v>85</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>535</v>
+        <v>85</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>287</v>
+        <v>138</v>
       </c>
       <c r="AQ60" t="s" s="2">
-        <v>288</v>
+        <v>387</v>
       </c>
       <c r="AR60" t="s" s="2">
-        <v>289</v>
+        <v>85</v>
       </c>
       <c r="AS60" t="s" s="2">
         <v>85</v>
@@ -9892,21 +9866,21 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>85</v>
+        <v>389</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>85</v>
@@ -9915,22 +9889,22 @@
         <v>85</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>364</v>
+        <v>184</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>537</v>
+        <v>390</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>366</v>
+        <v>391</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>538</v>
+        <v>392</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>368</v>
+        <v>393</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>85</v>
@@ -9955,13 +9929,13 @@
         <v>85</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>85</v>
+        <v>189</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>85</v>
+        <v>394</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>85</v>
+        <v>395</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>85</v>
@@ -9979,13 +9953,13 @@
         <v>85</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>85</v>
@@ -10006,27 +9980,27 @@
         <v>85</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>539</v>
+        <v>396</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>372</v>
+        <v>397</v>
       </c>
       <c r="AQ61" t="s" s="2">
-        <v>373</v>
+        <v>398</v>
       </c>
       <c r="AR61" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS61" t="s" s="2">
-        <v>374</v>
+        <v>399</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10037,7 +10011,7 @@
         <v>83</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>85</v>
@@ -10049,19 +10023,19 @@
         <v>85</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>184</v>
+        <v>86</v>
       </c>
       <c r="L62" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="M62" t="s" s="2">
         <v>541</v>
       </c>
-      <c r="M62" t="s" s="2">
-        <v>542</v>
-      </c>
       <c r="N62" t="s" s="2">
-        <v>543</v>
+        <v>450</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>389</v>
+        <v>451</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>85</v>
@@ -10086,13 +10060,13 @@
         <v>85</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>189</v>
+        <v>85</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>390</v>
+        <v>85</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>391</v>
+        <v>85</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>85</v>
@@ -10110,16 +10084,16 @@
         <v>85</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>544</v>
+        <v>85</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>107</v>
@@ -10140,282 +10114,20 @@
         <v>85</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>138</v>
+        <v>453</v>
       </c>
       <c r="AQ62" t="s" s="2">
-        <v>394</v>
+        <v>454</v>
       </c>
       <c r="AR62" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS62" t="s" s="2">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="63" hidden="true">
-      <c r="A63" t="s" s="2">
-        <v>545</v>
-      </c>
-      <c r="B63" t="s" s="2">
-        <v>545</v>
-      </c>
-      <c r="C63" s="2"/>
-      <c r="D63" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="E63" s="2"/>
-      <c r="F63" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="G63" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="H63" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="I63" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="J63" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="K63" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="L63" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="P63" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="Q63" s="2"/>
-      <c r="R63" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="S63" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="T63" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="U63" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="V63" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="W63" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="X63" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="Y63" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="Z63" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="AA63" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AB63" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AC63" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AD63" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AE63" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AF63" t="s" s="2">
-        <v>545</v>
-      </c>
-      <c r="AG63" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH63" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI63" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AJ63" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AK63" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AL63" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AM63" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AN63" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AO63" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="AP63" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="AQ63" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="AR63" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS63" t="s" s="2">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="64" hidden="true">
-      <c r="A64" t="s" s="2">
-        <v>546</v>
-      </c>
-      <c r="B64" t="s" s="2">
-        <v>546</v>
-      </c>
-      <c r="C64" s="2"/>
-      <c r="D64" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="E64" s="2"/>
-      <c r="F64" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="G64" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="H64" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="I64" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="J64" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="K64" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="L64" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>548</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="P64" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="Q64" s="2"/>
-      <c r="R64" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="S64" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="T64" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="U64" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="V64" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="W64" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="X64" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="Y64" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="Z64" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AA64" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AB64" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AC64" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AD64" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AE64" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AF64" t="s" s="2">
-        <v>546</v>
-      </c>
-      <c r="AG64" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH64" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI64" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AJ64" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AK64" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AL64" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AM64" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AN64" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AO64" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AP64" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="AQ64" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="AR64" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS64" t="s" s="2">
         <v>85</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AS64">
+  <autoFilter ref="A1:AS62">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -10425,7 +10137,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI63">
+  <conditionalFormatting sqref="A2:AI61">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.531</t>
+    <t>1.2.537</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-22T09:54:59+00:00</t>
+    <t>2025-02-24T13:20:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T13:20:37+00:00</t>
+    <t>2025-02-25T20:49:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.537</t>
+    <t>1.2.540</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-25T20:49:13+00:00</t>
+    <t>2025-03-11T10:08:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.540</t>
+    <t>1.3.557</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T10:08:33+00:00</t>
+    <t>2025-03-15T09:48:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.557</t>
+    <t>1.3.574</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-15T09:48:09+00:00</t>
+    <t>2025-03-22T10:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.574</t>
+    <t>1.3.575</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:33:38+00:00</t>
+    <t>2025-03-22T10:56:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.575</t>
+    <t>1.3.578</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:56:07+00:00</t>
+    <t>2025-03-23T10:22:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.578</t>
+    <t>1.3.580</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T10:22:17+00:00</t>
+    <t>2025-03-23T13:19:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
+++ b/docs/StructureDefinition-ObservationImagingResultRadNuc.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.580</t>
+    <t>1.4.588</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T13:19:29+00:00</t>
+    <t>2025-04-01T14:43:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
